--- a/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
@@ -674,40 +674,40 @@
     <t>The Override Price value in the grid is unchanged.</t>
   </si>
   <si>
+    <t>TC-CPR-OVR-029</t>
+  </si>
+  <si>
+    <t>The "Change Local Office" picker gates Select until a row is checked; Cancel applies nothing</t>
+  </si>
+  <si>
+    <t>On the Override screen with no location selected</t>
+  </si>
+  <si>
+    <t>1. Open the "Select a location" picker</t>
+  </si>
+  <si>
+    <t>The "Change Local Office" picker dialog opens.</t>
+  </si>
+  <si>
+    <t>2. Read the Select button before checking any row</t>
+  </si>
+  <si>
+    <t>The Select button is displayed disabled.</t>
+  </si>
+  <si>
+    <t>3. Search the office and check its row</t>
+  </si>
+  <si>
+    <t>The matching office row is displayed and its checkbox becomes checked.</t>
+  </si>
+  <si>
+    <t>4. Click Cancel</t>
+  </si>
+  <si>
+    <t>The picker is titled "Change Local Office"; Select is disabled until a row is checked, then enabled; Cancel closes it without applying a location</t>
+  </si>
+  <si>
     <t>TC-CPR-OVR-030</t>
-  </si>
-  <si>
-    <t>The "Change Local Office" picker gates Select until a row is checked; Cancel applies nothing</t>
-  </si>
-  <si>
-    <t>On the Override screen with no location selected</t>
-  </si>
-  <si>
-    <t>1. Open the "Select a location" picker</t>
-  </si>
-  <si>
-    <t>The "Change Local Office" picker dialog opens.</t>
-  </si>
-  <si>
-    <t>2. Read the Select button before checking any row</t>
-  </si>
-  <si>
-    <t>The Select button is displayed disabled.</t>
-  </si>
-  <si>
-    <t>3. Search the office and check its row</t>
-  </si>
-  <si>
-    <t>The matching office row is displayed and its checkbox becomes checked.</t>
-  </si>
-  <si>
-    <t>4. Click Cancel</t>
-  </si>
-  <si>
-    <t>The picker is titled "Change Local Office"; Select is disabled until a row is checked, then enabled; Cancel closes it without applying a location</t>
-  </si>
-  <si>
-    <t>TC-CPR-OVR-031</t>
   </si>
   <si>
     <t>Grid Options lists every column; toggling one hides its header and it persists across reload</t>
@@ -746,7 +746,7 @@
     <t>Grid Options exposes a toggle per column plus Reset to Default; hiding a column removes its header and the hidden state persists across a reload</t>
   </si>
   <si>
-    <t>TC-CPR-OVR-032</t>
+    <t>TC-CPR-OVR-031</t>
   </si>
   <si>
     <t>Export downloads a Product Group Overrides CSV directly (no dialog)</t>
@@ -785,7 +785,7 @@
     <t>The file contains a header row and at least one data row.</t>
   </si>
   <si>
-    <t>TC-CPR-OVR-033</t>
+    <t>TC-CPR-OVR-032</t>
   </si>
   <si>
     <t>Import opens the "Import All Pricing Overrides" dialog with a file input; Cancel closes it without uploading</t>
@@ -815,34 +815,34 @@
     <t>The dialog contains a file input control.</t>
   </si>
   <si>
+    <t>TC-CPR-OVR-033</t>
+  </si>
+  <si>
+    <t>Editing the Override Price on an inactive row auto-activates it</t>
+  </si>
+  <si>
+    <t>On the Override screen with location 1606 selected; anchor row at its default (active)</t>
+  </si>
+  <si>
+    <t>1. Set the anchor row inactive (staged only)</t>
+  </si>
+  <si>
+    <t>The Active checkbox becomes unchecked.</t>
+  </si>
+  <si>
+    <t>2. Edit the Override Price to a new value</t>
+  </si>
+  <si>
+    <t>The new value commits to the Override Price cell and the Active checkbox becomes checked again.</t>
+  </si>
+  <si>
+    <t>3. Observe Save</t>
+  </si>
+  <si>
+    <t>Editing the Override Price on an inactive row automatically re-activates it. (No commit - staged edit discarded on the next navigation.)</t>
+  </si>
+  <si>
     <t>TC-CPR-OVR-034</t>
-  </si>
-  <si>
-    <t>Editing the Override Price on an inactive row auto-activates it</t>
-  </si>
-  <si>
-    <t>On the Override screen with location 1606 selected; anchor row at its default (active)</t>
-  </si>
-  <si>
-    <t>1. Set the anchor row inactive (staged only)</t>
-  </si>
-  <si>
-    <t>The Active checkbox becomes unchecked.</t>
-  </si>
-  <si>
-    <t>2. Edit the Override Price to a new value</t>
-  </si>
-  <si>
-    <t>The new value commits to the Override Price cell and the Active checkbox becomes checked again.</t>
-  </si>
-  <si>
-    <t>3. Observe Save</t>
-  </si>
-  <si>
-    <t>Editing the Override Price on an inactive row automatically re-activates it. (No commit - staged edit discarded on the next navigation.)</t>
-  </si>
-  <si>
-    <t>TC-CPR-OVR-035</t>
   </si>
   <si>
     <t>Clicking a column header does not sort (no active sort state, row order unchanged)</t>
@@ -866,22 +866,22 @@
     <t>The Override grid headers are not sort triggers on this build - a header click sets no active sort state and does not reorder rows (consistent with the Search and Detail grids)</t>
   </si>
   <si>
+    <t>TC-CPR-OVR-035</t>
+  </si>
+  <si>
+    <t>Every row shows a Current Price value on office 1606 (no blank cell)</t>
+  </si>
+  <si>
+    <t>On the Override screen with location 1606 selected (USD data)</t>
+  </si>
+  <si>
+    <t>1. Read the Current Price cell of every visible row</t>
+  </si>
+  <si>
+    <t>Current Price renders a value for every row on office 1606 + USD - the blank / red-circle state does not occur here</t>
+  </si>
+  <si>
     <t>TC-CPR-OVR-036</t>
-  </si>
-  <si>
-    <t>Every row shows a Current Price value on office 1606 (no blank cell)</t>
-  </si>
-  <si>
-    <t>On the Override screen with location 1606 selected (USD data)</t>
-  </si>
-  <si>
-    <t>1. Read the Current Price cell of every visible row</t>
-  </si>
-  <si>
-    <t>Current Price renders a value for every row on office 1606 + USD - the blank / red-circle state does not occur here</t>
-  </si>
-  <si>
-    <t>TC-CPR-OVR-037</t>
   </si>
   <si>
     <t>Max Discount % accepts values up to the 100 cap (inclusive)</t>
@@ -917,7 +917,7 @@
     <t>4. Observe Save</t>
   </si>
   <si>
-    <t>TC-CPR-OVR-038</t>
+    <t>TC-CPR-OVR-037</t>
   </si>
   <si>
     <t>Every downloaded CSV row is well-formed with valid IDs, currency, 0/1 flags, and money fields</t>
@@ -938,7 +938,7 @@
     <t>Every row in the downloaded file has the full 9-column shape, a numeric Location Id and Product Group Id, a supported Currency (USD/CAD/MXN), 0/1 values in the Is Labor and Is Active flag columns, an always-populated Current Price money value, an Override Price that is either blank or a money value, and an Override Discount that is either blank or a plain decimal. The file is a tenant-wide dump (not scoped to the selected location); Product Group Name is free text and is not asserted for content</t>
   </si>
   <si>
-    <t>TC-CPR-OVR-061</t>
+    <t>TC-CPR-OVR-060</t>
   </si>
   <si>
     <t>A blank Override Price renders as an em-dash in a muted style, not an empty cell</t>
@@ -971,64 +971,64 @@
     <t>A blank/never-set Override Price renders the muted em-dash placeholder. Asserting empty-string would pass on the wrong render - the test asserts the em-dash explicitly (read-only bed; no mutation)</t>
   </si>
   <si>
+    <t>TC-CPR-OVR-065</t>
+  </si>
+  <si>
+    <t>Override Price rejects negative input (−5) with full rejection oracle</t>
+  </si>
+  <si>
+    <t>The value -5 is entered into the Override Price field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>-5 is rejected - the editor stays open, is invalid, red border, Save disabled. No error message is announced ([ ] displayed text is empty - defect #4). The editor is escapable via Tab (NOT a focus trap)</t>
+  </si>
+  <si>
     <t>TC-CPR-OVR-066</t>
   </si>
   <si>
-    <t>Override Price rejects negative input (−5) with full rejection oracle</t>
-  </si>
-  <si>
-    <t>The value -5 is entered into the Override Price field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>-5 is rejected - the editor stays open, is invalid, red border, Save disabled. No error message is announced ([ ] displayed text is empty - defect #4). The editor is escapable via Tab (NOT a focus trap)</t>
+    <t>Override Price rejects below-min boundary (−0.01)</t>
+  </si>
+  <si>
+    <t>The value -0.01 is entered into the Override Price field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>3. Assert rejection: committed=false, is invalid, Save disabled</t>
+  </si>
+  <si>
+    <t>-0.01 (BVA: smallest step below zero) is rejected with the standard rejection signature - editor keeps -0.01, Save DISABLED</t>
   </si>
   <si>
     <t>TC-CPR-OVR-067</t>
   </si>
   <si>
-    <t>Override Price rejects below-min boundary (−0.01)</t>
-  </si>
-  <si>
-    <t>The value -0.01 is entered into the Override Price field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>3. Assert rejection: committed=false, is invalid, Save disabled</t>
-  </si>
-  <si>
-    <t>-0.01 (BVA: smallest step below zero) is rejected with the standard rejection signature - editor keeps -0.01, Save DISABLED</t>
+    <t>Override Price accepts 3rd-decimal precision (0.001)</t>
+  </si>
+  <si>
+    <t>The value 0.001 is entered into the Override Price field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>3. Assert committed=true, observe displayedValue</t>
+  </si>
+  <si>
+    <t>0.001 commits (editor closes). "Pending verification" - decimal inputs are accepted per existing TCs; the exact display format for 3-decimal precision has not been confirmed (likely 0.00 due to 2-decimal rendering)</t>
   </si>
   <si>
     <t>TC-CPR-OVR-068</t>
   </si>
   <si>
-    <t>Override Price accepts 3rd-decimal precision (0.001)</t>
-  </si>
-  <si>
-    <t>The value 0.001 is entered into the Override Price field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>3. Assert committed=true, observe displayedValue</t>
-  </si>
-  <si>
-    <t>0.001 commits (editor closes). "Pending verification" - decimal inputs are accepted per existing TCs; the exact display format for 3-decimal precision has not been confirmed (likely 0.00 due to 2-decimal rendering)</t>
+    <t>Override Price accepts large value - no hard upper max (999999)</t>
+  </si>
+  <si>
+    <t>The value 999999 is entered into the Override Price field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>3. Assert committed=true, saveEnabled=true</t>
+  </si>
+  <si>
+    <t>999999 commits - the Override Price field has no hard upper maximum. Save enables (value changed from baseline 152.00)</t>
   </si>
   <si>
     <t>TC-CPR-OVR-069</t>
-  </si>
-  <si>
-    <t>Override Price accepts large value - no hard upper max (999999)</t>
-  </si>
-  <si>
-    <t>The value 999999 is entered into the Override Price field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>3. Assert committed=true, saveEnabled=true</t>
-  </si>
-  <si>
-    <t>999999 commits - the Override Price field has no hard upper maximum. Save enables (value changed from baseline 152.00)</t>
-  </si>
-  <si>
-    <t>TC-CPR-OVR-070</t>
   </si>
   <si>
     <t>Defect - Override Price silently commits 1.2.3 as 1.23 (multi-dot corruption)</t>
@@ -1058,61 +1058,61 @@
     <t>The defect is documented: the app accepts 1.2.3 as 1.23 instead of rejecting the malformed multi-dot input.</t>
   </si>
   <si>
+    <t>TC-CPR-OVR-070</t>
+  </si>
+  <si>
+    <t>Override Price with leading zeros (007) - zeros stripped</t>
+  </si>
+  <si>
+    <t>The value 007 is entered into the Override Price field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>007 commits with leading zeros stripped - displays as 7.00 (no % suffix). Save ENABLED</t>
+  </si>
+  <si>
     <t>TC-CPR-OVR-071</t>
   </si>
   <si>
-    <t>Override Price with leading zeros (007) - zeros stripped</t>
-  </si>
-  <si>
-    <t>The value 007 is entered into the Override Price field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>007 commits with leading zeros stripped - displays as 7.00 (no % suffix). Save ENABLED</t>
+    <t>Override Price with scientific notation (1e5)</t>
+  </si>
+  <si>
+    <t>The value 1e5 is entered into the Override Price field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>3. Observe whether committed or rejected</t>
+  </si>
+  <si>
+    <t>1e5 commits on Override Price - displays as 100,000.00. Save ENABLED. Max Discount % rejects 1e5 because the &gt;100 cap fires, not because the app refuses scientific notation; Override Price has no such cap, so it accepts the value</t>
   </si>
   <si>
     <t>TC-CPR-OVR-072</t>
   </si>
   <si>
-    <t>Override Price with scientific notation (1e5)</t>
-  </si>
-  <si>
-    <t>The value 1e5 is entered into the Override Price field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>3. Observe whether committed or rejected</t>
-  </si>
-  <si>
-    <t>1e5 commits on Override Price - displays as 100,000.00. Save ENABLED. Max Discount % rejects 1e5 because the &gt;100 cap fires, not because the app refuses scientific notation; Override Price has no such cap, so it accepts the value</t>
+    <t>Max Discount % accepts mid-range value (50)</t>
+  </si>
+  <si>
+    <t>The value 50 is entered into the Max Discount % field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>3. Assert committed=true, displayedValue=50.00 %, saveEnabled=true</t>
+  </si>
+  <si>
+    <t>50 commits and displays as 50.00 %. Save enables (changed from baseline)</t>
   </si>
   <si>
     <t>TC-CPR-OVR-073</t>
   </si>
   <si>
-    <t>Max Discount % accepts mid-range value (50)</t>
-  </si>
-  <si>
-    <t>The value 50 is entered into the Max Discount % field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>3. Assert committed=true, displayedValue=50.00 %, saveEnabled=true</t>
-  </si>
-  <si>
-    <t>50 commits and displays as 50.00 %. Save enables (changed from baseline)</t>
+    <t>Max Discount % rejects below-min boundary (−0.01)</t>
+  </si>
+  <si>
+    <t>The value -0.01 is entered into the Max Discount % field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>-0.01 (BVA: smallest step below the 0% floor) is rejected - editor keeps -0.01, Save DISABLED</t>
   </si>
   <si>
     <t>TC-CPR-OVR-074</t>
-  </si>
-  <si>
-    <t>Max Discount % rejects below-min boundary (−0.01)</t>
-  </si>
-  <si>
-    <t>The value -0.01 is entered into the Max Discount % field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>-0.01 (BVA: smallest step below the 0% floor) is rejected - editor keeps -0.01, Save DISABLED</t>
-  </si>
-  <si>
-    <t>TC-CPR-OVR-075</t>
   </si>
   <si>
     <t>Defect - 0.5 in Max Discount % displays as 50.00 % (100x multiplier bug)</t>
@@ -1155,129 +1155,129 @@
     <t>The comparison against the corrected display value of 0.50 % is recorded so a future fix is caught immediately.</t>
   </si>
   <si>
+    <t>TC-CPR-OVR-075</t>
+  </si>
+  <si>
+    <t>Max Discount % accepts just-below-cap boundary (99.99)</t>
+  </si>
+  <si>
+    <t>The value 99.99 is entered into the Max Discount % field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>3. Assert committed=true, displayedValue=99.99 %</t>
+  </si>
+  <si>
+    <t>99.99 commits and displays as 99.99 % (BVA: just below the inclusive 100 cap). Save ENABLED</t>
+  </si>
+  <si>
     <t>TC-CPR-OVR-076</t>
   </si>
   <si>
-    <t>Max Discount % accepts just-below-cap boundary (99.99)</t>
-  </si>
-  <si>
-    <t>The value 99.99 is entered into the Max Discount % field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>3. Assert committed=true, displayedValue=99.99 %</t>
-  </si>
-  <si>
-    <t>99.99 commits and displays as 99.99 % (BVA: just below the inclusive 100 cap). Save ENABLED</t>
+    <t>Max Discount % rejects above-cap (100.01) with full oracle - supersedes skipped TC-023</t>
   </si>
   <si>
     <t>TC-CPR-OVR-077</t>
   </si>
   <si>
-    <t>Max Discount % rejects above-cap (100.01) with full oracle - supersedes skipped TC-023</t>
+    <t>Defect - abc blanks Max Discount % to em-dash with Save enabled</t>
+  </si>
+  <si>
+    <t>The characters abc are entered into the Max Discount % field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>3. Assert the DEFECT: committed=true, displayedValue=-, saveEnabled=true</t>
+  </si>
+  <si>
+    <t>The cell blanks to an em-dash, the editor closes, and the Save button stays enabled.</t>
+  </si>
+  <si>
+    <t>The defect is documented: non-numeric input blanks the cell instead of being rejected.</t>
+  </si>
+  <si>
+    <t>5. abc commits (editor closes) and blanks the cell to -. Save stays ENABLED despite the displayed value matching the original baseline. Two bugs: (1) non-numeric input should be rejected, not committed</t>
+  </si>
+  <si>
+    <t>The cell displays an em-dash after the non-numeric entry, with the value neither rejected nor retained.</t>
+  </si>
+  <si>
+    <t>6. (2) Save enables on what is effectively an unchanged result (baseline was already). When fixed, committed will become false (proper rejection) and/or saveEnabled will become false</t>
+  </si>
+  <si>
+    <t>The Save button stays enabled even though the displayed value matches the original baseline.</t>
   </si>
   <si>
     <t>TC-CPR-OVR-078</t>
   </si>
   <si>
-    <t>Defect - abc blanks Max Discount % to em-dash with Save enabled</t>
-  </si>
-  <si>
-    <t>The characters abc are entered into the Max Discount % field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>3. Assert the DEFECT: committed=true, displayedValue=-, saveEnabled=true</t>
-  </si>
-  <si>
-    <t>The cell blanks to an em-dash, the editor closes, and the Save button stays enabled.</t>
-  </si>
-  <si>
-    <t>The defect is documented: non-numeric input blanks the cell instead of being rejected.</t>
-  </si>
-  <si>
-    <t>5. abc commits (editor closes) and blanks the cell to -. Save stays ENABLED despite the displayed value matching the original baseline. Two bugs: (1) non-numeric input should be rejected, not committed</t>
-  </si>
-  <si>
-    <t>The cell displays an em-dash after the non-numeric entry, with the value neither rejected nor retained.</t>
-  </si>
-  <si>
-    <t>6. (2) Save enables on what is effectively an unchanged result (baseline was already). When fixed, committed will become false (proper rejection) and/or saveEnabled will become false</t>
-  </si>
-  <si>
-    <t>The Save button stays enabled even though the displayed value matches the original baseline.</t>
+    <t>Defect - 1.2.3 in Max Discount % silently commits as 1.23 %</t>
+  </si>
+  <si>
+    <t>2. Call (real keyboard input)</t>
+  </si>
+  <si>
+    <t>The characters 1.2.3 are typed into the Max Discount % field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>3. Assert the DEFECT: committed=true, displayedValue=1.23 %, saveEnabled=true</t>
+  </si>
+  <si>
+    <t>The value commits as 1.23 %, the editor closes, and the Save button becomes enabled.</t>
+  </si>
+  <si>
+    <t>4. "Expected (asserting the BUG - test FAILS when app is fixed)": 1.2.3 commits as 1.23 % - the browser swallows the second dot during real keyboard typing, producing a plausible-looking but corrupted value. No warning, no rejection. Note: Override Price renders the same bug as 1.23 (no % suffix) - the two fields format differently. When fixed, this input should be rejected</t>
+  </si>
+  <si>
+    <t>The defect is documented: the app accepts 1.2.3 as 1.23 % instead of rejecting the malformed multi-dot input.</t>
   </si>
   <si>
     <t>TC-CPR-OVR-079</t>
   </si>
   <si>
-    <t>Defect - 1.2.3 in Max Discount % silently commits as 1.23 %</t>
-  </si>
-  <si>
-    <t>2. Call (real keyboard input)</t>
-  </si>
-  <si>
-    <t>The characters 1.2.3 are typed into the Max Discount % field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>3. Assert the DEFECT: committed=true, displayedValue=1.23 %, saveEnabled=true</t>
-  </si>
-  <si>
-    <t>The value commits as 1.23 %, the editor closes, and the Save button becomes enabled.</t>
-  </si>
-  <si>
-    <t>4. "Expected (asserting the BUG - test FAILS when app is fixed)": 1.2.3 commits as 1.23 % - the browser swallows the second dot during real keyboard typing, producing a plausible-looking but corrupted value. No warning, no rejection. Note: Override Price renders the same bug as 1.23 (no % suffix) - the two fields format differently. When fixed, this input should be rejected</t>
-  </si>
-  <si>
-    <t>The defect is documented: the app accepts 1.2.3 as 1.23 % instead of rejecting the malformed multi-dot input.</t>
+    <t>Max Discount % rejects scientific notation (1e5)</t>
+  </si>
+  <si>
+    <t>The value 1e5 is entered into the Max Discount % field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>1e5 is rejected - the editor stays open, is invalid, Save disabled. Verified on Equipment Max Discount %</t>
   </si>
   <si>
     <t>TC-CPR-OVR-080</t>
   </si>
   <si>
-    <t>Max Discount % rejects scientific notation (1e5)</t>
-  </si>
-  <si>
-    <t>The value 1e5 is entered into the Max Discount % field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>1e5 is rejected - the editor stays open, is invalid, Save disabled. Verified on Equipment Max Discount %</t>
+    <t>Max Discount % strips leading zeros (007 -&gt; 7.00 %)</t>
+  </si>
+  <si>
+    <t>The value 007 is entered into the Max Discount % field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>3. Assert committed=true, displayedValue=7.00 %, saveEnabled=true</t>
+  </si>
+  <si>
+    <t>007 commits as 7.00 % - leading zeros are stripped. Save enables</t>
   </si>
   <si>
     <t>TC-CPR-OVR-081</t>
   </si>
   <si>
-    <t>Max Discount % strips leading zeros (007 -&gt; 7.00 %)</t>
-  </si>
-  <si>
-    <t>The value 007 is entered into the Max Discount % field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>3. Assert committed=true, displayedValue=7.00 %, saveEnabled=true</t>
-  </si>
-  <si>
-    <t>007 commits as 7.00 % - leading zeros are stripped. Save enables</t>
+    <t>Max Discount % revert-to-original disables Save</t>
+  </si>
+  <si>
+    <t>On the Override screen, office 4107 selected, Equipment tab active. Max Discount % baseline is - (empty)</t>
+  </si>
+  <si>
+    <t>The value 50 is entered, then the field is cleared and reverted to the original empty value.</t>
+  </si>
+  <si>
+    <t>3. Assert saveEnabledAfterEdit=true, saveDisabledAfterRevert=true</t>
+  </si>
+  <si>
+    <t>Editing Max Discount % to 50 enables Save; reverting to the original empty value via Ctrl+A -&gt; Delete -&gt; Enter disables Save (true revert-to-original confirmed, no net change)</t>
   </si>
   <si>
     <t>TC-CPR-OVR-082</t>
   </si>
   <si>
-    <t>Max Discount % revert-to-original disables Save</t>
-  </si>
-  <si>
-    <t>On the Override screen, office 4107 selected, Equipment tab active. Max Discount % baseline is - (empty)</t>
-  </si>
-  <si>
-    <t>The value 50 is entered, then the field is cleared and reverted to the original empty value.</t>
-  </si>
-  <si>
-    <t>3. Assert saveEnabledAfterEdit=true, saveDisabledAfterRevert=true</t>
-  </si>
-  <si>
-    <t>Editing Max Discount % to 50 enables Save; reverting to the original empty value via Ctrl+A -&gt; Delete -&gt; Enter disables Save (true revert-to-original confirmed, no net change)</t>
-  </si>
-  <si>
-    <t>TC-CPR-OVR-083</t>
-  </si>
-  <si>
     <t>Active toggle-then-revert disables Save</t>
   </si>
   <si>
@@ -1296,57 +1296,57 @@
     <t>Toggling Active away from its saved state enables Save; toggling it back to the original state disables Save (no net change, no save needed)</t>
   </si>
   <si>
+    <t>TC-CPR-OVR-116</t>
+  </si>
+  <si>
+    <t>Import rejects a CSV with an empty Override Price - whole-file rejection (known defect)</t>
+  </si>
+  <si>
+    <t>Skipped</t>
+  </si>
+  <si>
+    <t>On the Override screen with office 1606 selected; the import dialog open</t>
+  </si>
+  <si>
+    <t>1. Open the Import dialog via the toolbar "Import" button</t>
+  </si>
+  <si>
+    <t>The Import dialog opens.</t>
+  </si>
+  <si>
+    <t>2. Prepare and attach a CSV file containing at least one row with an empty Override Price cell (the minimum reproduction for this known defect)</t>
+  </si>
+  <si>
+    <t>The file is attached and the Upload button becomes enabled.</t>
+  </si>
+  <si>
+    <t>3. The upload fires (auto-submit on file-choose per agent-mistakes.md:206)</t>
+  </si>
+  <si>
+    <t>The upload request fires automatically.</t>
+  </si>
+  <si>
+    <t>4. Assert: the import is REJECTED (not success)</t>
+  </si>
+  <si>
+    <t>The import is rejected.</t>
+  </si>
+  <si>
+    <t>5. the grid is unchanged (no rows modified)</t>
+  </si>
+  <si>
+    <t>The grid rows remain unchanged.</t>
+  </si>
+  <si>
+    <t>6. a rejection indicator is visible (error message or the dialog remains open with an error state)</t>
+  </si>
+  <si>
+    <t>A rejection indicator is visible on screen confirming the import was not successful.</t>
+  </si>
+  <si>
     <t>TC-CPR-OVR-117</t>
   </si>
   <si>
-    <t>Import rejects a CSV with an empty Override Price - whole-file rejection (known defect)</t>
-  </si>
-  <si>
-    <t>Skipped</t>
-  </si>
-  <si>
-    <t>On the Override screen with office 1606 selected; the import dialog open</t>
-  </si>
-  <si>
-    <t>1. Open the Import dialog via the toolbar "Import" button</t>
-  </si>
-  <si>
-    <t>The Import dialog opens.</t>
-  </si>
-  <si>
-    <t>2. Prepare and attach a CSV file containing at least one row with an empty Override Price cell (the minimum reproduction for this known defect)</t>
-  </si>
-  <si>
-    <t>The file is attached and the Upload button becomes enabled.</t>
-  </si>
-  <si>
-    <t>3. The upload fires (auto-submit on file-choose per agent-mistakes.md:206)</t>
-  </si>
-  <si>
-    <t>The upload request fires automatically.</t>
-  </si>
-  <si>
-    <t>4. Assert: the import is REJECTED (not success)</t>
-  </si>
-  <si>
-    <t>The import is rejected.</t>
-  </si>
-  <si>
-    <t>5. the grid is unchanged (no rows modified)</t>
-  </si>
-  <si>
-    <t>The grid rows remain unchanged.</t>
-  </si>
-  <si>
-    <t>6. a rejection indicator is visible (error message or the dialog remains open with an error state)</t>
-  </si>
-  <si>
-    <t>A rejection indicator is visible on screen confirming the import was not successful.</t>
-  </si>
-  <si>
-    <t>TC-CPR-OVR-118</t>
-  </si>
-  <si>
     <t>Tab-switch from dirty Equipment grid to Labor - unsaved changes persists without a guard dialog</t>
   </si>
   <si>
@@ -1386,7 +1386,7 @@
     <t>Save remains enabled confirming the unsaved changes persisted across the tab round-trip.</t>
   </si>
   <si>
-    <t>TC-CPR-OVR-120</t>
+    <t>TC-CPR-OVR-119</t>
   </si>
   <si>
     <t>Tab-switch from dirty Labor grid to Equipment - unsaved changes persists without a guard dialog</t>
@@ -1416,7 +1416,7 @@
     <t>5. Save is still enabled (unsaved changes preserved across tab round-trip)</t>
   </si>
   <si>
-    <t>TC-CPR-OVR-138</t>
+    <t>TC-CPR-OVR-137</t>
   </si>
   <si>
     <t>The export tolerates rows with no Override Price and never drops them</t>
@@ -1443,7 +1443,7 @@
     <t>The file is allowed to contain rows with no Override Price and they are never dropped, while the vast majority of rows do carry one. Asserting the current contract rather than the desired one: the app's own import rejects these rows, so a test demanding a price on every row would fail on every run today</t>
   </si>
   <si>
-    <t>TC-CPR-OVR-152</t>
+    <t>TC-CPR-OVR-151</t>
   </si>
   <si>
     <t>Raw export with an empty Override Price row is rejected and changes nothing</t>
@@ -1491,7 +1491,7 @@
     <t>Pass:59 Fail:0 Skipped:1 Blocked:1</t>
   </si>
   <si>
-    <t>Last Updated: 2026-07-27</t>
+    <t>Last Updated: 2026-07-30</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2418" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2418" uniqueCount="476">
   <si>
     <t>TC ID</t>
   </si>
@@ -78,7 +78,7 @@
     <t>Automated</t>
   </si>
   <si>
-    <t>Pass</t>
+    <t/>
   </si>
   <si>
     <t>Authenticated on office 1604</t>
@@ -88,9 +88,6 @@
   </si>
   <si>
     <t>The Product Group Override screen loads and is displayed.</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>2. Read the active tab</t>
@@ -1488,10 +1485,10 @@
     <t>Automated: 61 / Pending: 0</t>
   </si>
   <si>
-    <t>Pass:59 Fail:0 Skipped:1 Blocked:1</t>
-  </si>
-  <si>
-    <t>Last Updated: 2026-07-30</t>
+    <t>Not run in this delivery</t>
+  </si>
+  <si>
+    <t>Last Updated: 2026-08-07</t>
   </si>
 </sst>
 </file>
@@ -1890,7 +1887,7 @@
     <col min="5" max="5" width="80" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="36" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
     <col min="10" max="13" width="80" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1973,56 +1970,56 @@
         <v>24</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
         <v>25</v>
       </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>26</v>
       </c>
-      <c r="L3" t="s">
-        <v>27</v>
-      </c>
       <c r="M3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
         <v>28</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -2046,65 +2043,65 @@
         <v>21</v>
       </c>
       <c r="J4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" t="s">
         <v>30</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>31</v>
       </c>
-      <c r="L4" t="s">
-        <v>32</v>
-      </c>
       <c r="M4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" t="s">
         <v>33</v>
       </c>
-      <c r="L5" t="s">
-        <v>34</v>
-      </c>
       <c r="M5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
         <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>36</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
@@ -2113,7 +2110,7 @@
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -2128,106 +2125,106 @@
         <v>21</v>
       </c>
       <c r="J6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" t="s">
         <v>38</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>39</v>
       </c>
-      <c r="L6" t="s">
-        <v>40</v>
-      </c>
       <c r="M6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K7" t="s">
+        <v>40</v>
+      </c>
+      <c r="L7" t="s">
         <v>41</v>
       </c>
-      <c r="L7" t="s">
-        <v>42</v>
-      </c>
       <c r="M7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8" t="s">
         <v>43</v>
       </c>
-      <c r="L8" t="s">
-        <v>44</v>
-      </c>
       <c r="M8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s">
         <v>45</v>
-      </c>
-      <c r="B9" t="s">
-        <v>46</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
@@ -2236,7 +2233,7 @@
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -2251,106 +2248,106 @@
         <v>21</v>
       </c>
       <c r="J9" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" t="s">
         <v>48</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>49</v>
       </c>
-      <c r="L9" t="s">
-        <v>50</v>
-      </c>
       <c r="M9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K11" t="s">
+        <v>51</v>
+      </c>
+      <c r="L11" t="s">
         <v>52</v>
       </c>
-      <c r="L11" t="s">
-        <v>53</v>
-      </c>
       <c r="M11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" t="s">
         <v>54</v>
-      </c>
-      <c r="B12" t="s">
-        <v>55</v>
       </c>
       <c r="C12" t="s">
         <v>15</v>
@@ -2374,24 +2371,24 @@
         <v>21</v>
       </c>
       <c r="J12" t="s">
+        <v>55</v>
+      </c>
+      <c r="K12" t="s">
         <v>56</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
         <v>57</v>
       </c>
-      <c r="L12" t="s">
-        <v>58</v>
-      </c>
       <c r="M12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" t="s">
         <v>59</v>
-      </c>
-      <c r="B13" t="s">
-        <v>60</v>
       </c>
       <c r="C13" t="s">
         <v>15</v>
@@ -2415,24 +2412,24 @@
         <v>21</v>
       </c>
       <c r="J13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K13" t="s">
+        <v>60</v>
+      </c>
+      <c r="L13" t="s">
         <v>61</v>
       </c>
-      <c r="L13" t="s">
-        <v>62</v>
-      </c>
       <c r="M13" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" t="s">
         <v>63</v>
-      </c>
-      <c r="B14" t="s">
-        <v>64</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -2456,24 +2453,24 @@
         <v>21</v>
       </c>
       <c r="J14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K14" t="s">
+        <v>64</v>
+      </c>
+      <c r="L14" t="s">
         <v>65</v>
       </c>
-      <c r="L14" t="s">
-        <v>66</v>
-      </c>
       <c r="M14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" t="s">
         <v>67</v>
-      </c>
-      <c r="B15" t="s">
-        <v>68</v>
       </c>
       <c r="C15" t="s">
         <v>15</v>
@@ -2497,106 +2494,106 @@
         <v>21</v>
       </c>
       <c r="J15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K15" t="s">
+        <v>68</v>
+      </c>
+      <c r="L15" t="s">
         <v>69</v>
       </c>
-      <c r="L15" t="s">
-        <v>70</v>
-      </c>
       <c r="M15" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K17" t="s">
+        <v>71</v>
+      </c>
+      <c r="L17" t="s">
         <v>72</v>
       </c>
-      <c r="L17" t="s">
-        <v>73</v>
-      </c>
       <c r="M17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" t="s">
         <v>74</v>
-      </c>
-      <c r="B18" t="s">
-        <v>75</v>
       </c>
       <c r="C18" t="s">
         <v>15</v>
@@ -2620,65 +2617,65 @@
         <v>21</v>
       </c>
       <c r="J18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K18" t="s">
+        <v>75</v>
+      </c>
+      <c r="L18" t="s">
         <v>76</v>
       </c>
-      <c r="L18" t="s">
-        <v>77</v>
-      </c>
       <c r="M18" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K19" t="s">
+        <v>77</v>
+      </c>
+      <c r="L19" t="s">
         <v>78</v>
       </c>
-      <c r="L19" t="s">
-        <v>79</v>
-      </c>
       <c r="M19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" t="s">
         <v>80</v>
-      </c>
-      <c r="B20" t="s">
-        <v>81</v>
       </c>
       <c r="C20" t="s">
         <v>15</v>
@@ -2702,106 +2699,106 @@
         <v>21</v>
       </c>
       <c r="J20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K20" t="s">
+        <v>81</v>
+      </c>
+      <c r="L20" t="s">
         <v>82</v>
       </c>
-      <c r="L20" t="s">
-        <v>83</v>
-      </c>
       <c r="M20" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E21" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F21" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G21" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H21" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I21" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J21" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K21" t="s">
+        <v>83</v>
+      </c>
+      <c r="L21" t="s">
         <v>84</v>
       </c>
-      <c r="L21" t="s">
-        <v>85</v>
-      </c>
       <c r="M21" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" t="s">
         <v>87</v>
-      </c>
-      <c r="B23" t="s">
-        <v>88</v>
       </c>
       <c r="C23" t="s">
         <v>15</v>
@@ -2825,65 +2822,65 @@
         <v>21</v>
       </c>
       <c r="J23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K23" t="s">
+        <v>88</v>
+      </c>
+      <c r="L23" t="s">
         <v>89</v>
       </c>
-      <c r="L23" t="s">
-        <v>90</v>
-      </c>
       <c r="M23" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K24" t="s">
+        <v>90</v>
+      </c>
+      <c r="L24" t="s">
         <v>91</v>
       </c>
-      <c r="L24" t="s">
-        <v>92</v>
-      </c>
       <c r="M24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" t="s">
         <v>93</v>
-      </c>
-      <c r="B25" t="s">
-        <v>94</v>
       </c>
       <c r="C25" t="s">
         <v>15</v>
@@ -2892,7 +2889,7 @@
         <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
@@ -2907,106 +2904,106 @@
         <v>21</v>
       </c>
       <c r="J25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K25" t="s">
+        <v>95</v>
+      </c>
+      <c r="L25" t="s">
         <v>96</v>
       </c>
-      <c r="L25" t="s">
-        <v>97</v>
-      </c>
       <c r="M25" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K27" t="s">
+        <v>98</v>
+      </c>
+      <c r="L27" t="s">
         <v>99</v>
       </c>
-      <c r="L27" t="s">
-        <v>100</v>
-      </c>
       <c r="M27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" t="s">
         <v>101</v>
-      </c>
-      <c r="B28" t="s">
-        <v>102</v>
       </c>
       <c r="C28" t="s">
         <v>15</v>
@@ -3015,7 +3012,7 @@
         <v>16</v>
       </c>
       <c r="E28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F28" t="s">
         <v>18</v>
@@ -3030,106 +3027,106 @@
         <v>21</v>
       </c>
       <c r="J28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K28" t="s">
+        <v>103</v>
+      </c>
+      <c r="L28" t="s">
         <v>104</v>
       </c>
-      <c r="L28" t="s">
-        <v>105</v>
-      </c>
       <c r="M28" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C29" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D29" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E29" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F29" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G29" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H29" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I29" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J29" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M29" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K30" t="s">
+        <v>106</v>
+      </c>
+      <c r="L30" t="s">
         <v>107</v>
       </c>
-      <c r="L30" t="s">
-        <v>108</v>
-      </c>
       <c r="M30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" t="s">
         <v>109</v>
-      </c>
-      <c r="B31" t="s">
-        <v>110</v>
       </c>
       <c r="C31" t="s">
         <v>15</v>
@@ -3138,7 +3135,7 @@
         <v>16</v>
       </c>
       <c r="E31" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F31" t="s">
         <v>18</v>
@@ -3153,65 +3150,65 @@
         <v>21</v>
       </c>
       <c r="J31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K31" t="s">
+        <v>111</v>
+      </c>
+      <c r="L31" t="s">
         <v>112</v>
       </c>
-      <c r="L31" t="s">
-        <v>113</v>
-      </c>
       <c r="M31" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K32" t="s">
+        <v>113</v>
+      </c>
+      <c r="L32" t="s">
         <v>114</v>
       </c>
-      <c r="L32" t="s">
-        <v>115</v>
-      </c>
       <c r="M32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" t="s">
         <v>116</v>
-      </c>
-      <c r="B33" t="s">
-        <v>117</v>
       </c>
       <c r="C33" t="s">
         <v>15</v>
@@ -3235,65 +3232,65 @@
         <v>21</v>
       </c>
       <c r="J33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K33" t="s">
+        <v>117</v>
+      </c>
+      <c r="L33" t="s">
         <v>118</v>
       </c>
-      <c r="L33" t="s">
-        <v>119</v>
-      </c>
       <c r="M33" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L34" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>120</v>
+      </c>
+      <c r="B35" t="s">
         <v>121</v>
-      </c>
-      <c r="B35" t="s">
-        <v>122</v>
       </c>
       <c r="C35" t="s">
         <v>15</v>
@@ -3317,65 +3314,65 @@
         <v>21</v>
       </c>
       <c r="J35" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K35" t="s">
+        <v>122</v>
+      </c>
+      <c r="L35" t="s">
         <v>123</v>
       </c>
-      <c r="L35" t="s">
-        <v>124</v>
-      </c>
       <c r="M35" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K36" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>125</v>
+      </c>
+      <c r="B37" t="s">
         <v>126</v>
-      </c>
-      <c r="B37" t="s">
-        <v>127</v>
       </c>
       <c r="C37" t="s">
         <v>15</v>
@@ -3399,65 +3396,65 @@
         <v>21</v>
       </c>
       <c r="J37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K37" t="s">
+        <v>127</v>
+      </c>
+      <c r="L37" t="s">
         <v>128</v>
       </c>
-      <c r="L37" t="s">
-        <v>129</v>
-      </c>
       <c r="M37" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K38" t="s">
+        <v>129</v>
+      </c>
+      <c r="L38" t="s">
         <v>130</v>
       </c>
-      <c r="L38" t="s">
-        <v>131</v>
-      </c>
       <c r="M38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>131</v>
+      </c>
+      <c r="B39" t="s">
         <v>132</v>
-      </c>
-      <c r="B39" t="s">
-        <v>133</v>
       </c>
       <c r="C39" t="s">
         <v>15</v>
@@ -3481,65 +3478,65 @@
         <v>21</v>
       </c>
       <c r="J39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K39" t="s">
+        <v>133</v>
+      </c>
+      <c r="L39" t="s">
         <v>134</v>
       </c>
-      <c r="L39" t="s">
-        <v>135</v>
-      </c>
       <c r="M39" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K40" t="s">
+        <v>135</v>
+      </c>
+      <c r="L40" t="s">
         <v>136</v>
       </c>
-      <c r="L40" t="s">
-        <v>137</v>
-      </c>
       <c r="M40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>137</v>
+      </c>
+      <c r="B41" t="s">
         <v>138</v>
-      </c>
-      <c r="B41" t="s">
-        <v>139</v>
       </c>
       <c r="C41" t="s">
         <v>15</v>
@@ -3563,65 +3560,65 @@
         <v>21</v>
       </c>
       <c r="J41" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K41" t="s">
+        <v>139</v>
+      </c>
+      <c r="L41" t="s">
         <v>140</v>
       </c>
-      <c r="L41" t="s">
-        <v>141</v>
-      </c>
       <c r="M41" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K42" t="s">
+        <v>141</v>
+      </c>
+      <c r="L42" t="s">
         <v>142</v>
       </c>
-      <c r="L42" t="s">
-        <v>143</v>
-      </c>
       <c r="M42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>143</v>
+      </c>
+      <c r="B43" t="s">
         <v>144</v>
-      </c>
-      <c r="B43" t="s">
-        <v>145</v>
       </c>
       <c r="C43" t="s">
         <v>15</v>
@@ -3645,65 +3642,65 @@
         <v>21</v>
       </c>
       <c r="J43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K43" t="s">
+        <v>145</v>
+      </c>
+      <c r="L43" t="s">
         <v>146</v>
       </c>
-      <c r="L43" t="s">
-        <v>147</v>
-      </c>
       <c r="M43" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K44" t="s">
+        <v>147</v>
+      </c>
+      <c r="L44" t="s">
         <v>148</v>
       </c>
-      <c r="L44" t="s">
-        <v>149</v>
-      </c>
       <c r="M44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>149</v>
+      </c>
+      <c r="B45" t="s">
         <v>150</v>
-      </c>
-      <c r="B45" t="s">
-        <v>151</v>
       </c>
       <c r="C45" t="s">
         <v>15</v>
@@ -3727,65 +3724,65 @@
         <v>21</v>
       </c>
       <c r="J45" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K45" t="s">
+        <v>151</v>
+      </c>
+      <c r="L45" t="s">
         <v>152</v>
       </c>
-      <c r="L45" t="s">
-        <v>153</v>
-      </c>
       <c r="M45" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B46" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D46" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E46" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F46" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G46" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H46" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I46" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J46" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K46" t="s">
+        <v>153</v>
+      </c>
+      <c r="L46" t="s">
         <v>154</v>
       </c>
-      <c r="L46" t="s">
-        <v>155</v>
-      </c>
       <c r="M46" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>155</v>
+      </c>
+      <c r="B47" t="s">
         <v>156</v>
-      </c>
-      <c r="B47" t="s">
-        <v>157</v>
       </c>
       <c r="C47" t="s">
         <v>15</v>
@@ -3794,7 +3791,7 @@
         <v>16</v>
       </c>
       <c r="E47" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F47" t="s">
         <v>18</v>
@@ -3809,24 +3806,24 @@
         <v>21</v>
       </c>
       <c r="J47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K47" t="s">
+        <v>158</v>
+      </c>
+      <c r="L47" t="s">
         <v>159</v>
       </c>
-      <c r="L47" t="s">
-        <v>160</v>
-      </c>
       <c r="M47" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>160</v>
+      </c>
+      <c r="B48" t="s">
         <v>161</v>
-      </c>
-      <c r="B48" t="s">
-        <v>162</v>
       </c>
       <c r="C48" t="s">
         <v>15</v>
@@ -3847,109 +3844,109 @@
         <v>20</v>
       </c>
       <c r="I48" t="s">
+        <v>162</v>
+      </c>
+      <c r="J48" t="s">
         <v>163</v>
       </c>
-      <c r="J48" t="s">
+      <c r="K48" t="s">
         <v>164</v>
       </c>
-      <c r="K48" t="s">
+      <c r="L48" t="s">
         <v>165</v>
       </c>
-      <c r="L48" t="s">
+      <c r="M48" t="s">
         <v>166</v>
-      </c>
-      <c r="M48" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K49" t="s">
+        <v>167</v>
+      </c>
+      <c r="L49" t="s">
         <v>168</v>
       </c>
-      <c r="L49" t="s">
-        <v>169</v>
-      </c>
       <c r="M49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B50" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C50" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D50" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E50" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F50" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G50" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H50" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I50" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J50" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K50" t="s">
+        <v>169</v>
+      </c>
+      <c r="L50" t="s">
         <v>170</v>
       </c>
-      <c r="L50" t="s">
-        <v>171</v>
-      </c>
       <c r="M50" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>171</v>
+      </c>
+      <c r="B51" t="s">
         <v>172</v>
-      </c>
-      <c r="B51" t="s">
-        <v>173</v>
       </c>
       <c r="C51" t="s">
         <v>15</v>
@@ -3973,65 +3970,65 @@
         <v>21</v>
       </c>
       <c r="J51" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K51" t="s">
+        <v>173</v>
+      </c>
+      <c r="L51" t="s">
         <v>174</v>
       </c>
-      <c r="L51" t="s">
-        <v>175</v>
-      </c>
       <c r="M51" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B52" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C52" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D52" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E52" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F52" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G52" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H52" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I52" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J52" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K52" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L52" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M52" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>176</v>
+      </c>
+      <c r="B53" t="s">
         <v>177</v>
-      </c>
-      <c r="B53" t="s">
-        <v>178</v>
       </c>
       <c r="C53" t="s">
         <v>15</v>
@@ -4055,147 +4052,147 @@
         <v>21</v>
       </c>
       <c r="J53" t="s">
+        <v>178</v>
+      </c>
+      <c r="K53" t="s">
         <v>179</v>
       </c>
-      <c r="K53" t="s">
+      <c r="L53" t="s">
         <v>180</v>
       </c>
-      <c r="L53" t="s">
-        <v>181</v>
-      </c>
       <c r="M53" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B54" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C54" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D54" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E54" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F54" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G54" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H54" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I54" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J54" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K54" t="s">
+        <v>181</v>
+      </c>
+      <c r="L54" t="s">
         <v>182</v>
       </c>
-      <c r="L54" t="s">
-        <v>183</v>
-      </c>
       <c r="M54" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B55" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C55" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D55" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E55" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F55" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G55" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H55" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I55" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J55" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K55" t="s">
+        <v>183</v>
+      </c>
+      <c r="L55" t="s">
         <v>184</v>
       </c>
-      <c r="L55" t="s">
-        <v>185</v>
-      </c>
       <c r="M55" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B56" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C56" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E56" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F56" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G56" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H56" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I56" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J56" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K56" t="s">
+        <v>185</v>
+      </c>
+      <c r="L56" t="s">
         <v>186</v>
       </c>
-      <c r="L56" t="s">
-        <v>187</v>
-      </c>
       <c r="M56" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>187</v>
+      </c>
+      <c r="B57" t="s">
         <v>188</v>
-      </c>
-      <c r="B57" t="s">
-        <v>189</v>
       </c>
       <c r="C57" t="s">
         <v>15</v>
@@ -4219,106 +4216,106 @@
         <v>21</v>
       </c>
       <c r="J57" t="s">
+        <v>189</v>
+      </c>
+      <c r="K57" t="s">
         <v>190</v>
       </c>
-      <c r="K57" t="s">
+      <c r="L57" t="s">
         <v>191</v>
       </c>
-      <c r="L57" t="s">
-        <v>192</v>
-      </c>
       <c r="M57" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B58" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C58" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D58" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E58" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F58" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G58" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H58" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I58" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J58" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K58" t="s">
+        <v>192</v>
+      </c>
+      <c r="L58" t="s">
         <v>193</v>
       </c>
-      <c r="L58" t="s">
-        <v>194</v>
-      </c>
       <c r="M58" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B59" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C59" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D59" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E59" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F59" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G59" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H59" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I59" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J59" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K59" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L59" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M59" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>195</v>
+      </c>
+      <c r="B60" t="s">
         <v>196</v>
-      </c>
-      <c r="B60" t="s">
-        <v>197</v>
       </c>
       <c r="C60" t="s">
         <v>15</v>
@@ -4342,106 +4339,106 @@
         <v>21</v>
       </c>
       <c r="J60" t="s">
+        <v>197</v>
+      </c>
+      <c r="K60" t="s">
+        <v>190</v>
+      </c>
+      <c r="L60" t="s">
         <v>198</v>
       </c>
-      <c r="K60" t="s">
-        <v>191</v>
-      </c>
-      <c r="L60" t="s">
-        <v>199</v>
-      </c>
       <c r="M60" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B61" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C61" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D61" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E61" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F61" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G61" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H61" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I61" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J61" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K61" t="s">
+        <v>199</v>
+      </c>
+      <c r="L61" t="s">
         <v>200</v>
       </c>
-      <c r="L61" t="s">
-        <v>201</v>
-      </c>
       <c r="M61" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B62" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C62" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D62" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E62" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F62" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G62" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H62" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I62" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J62" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K62" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L62" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M62" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>202</v>
+      </c>
+      <c r="B63" t="s">
         <v>203</v>
-      </c>
-      <c r="B63" t="s">
-        <v>204</v>
       </c>
       <c r="C63" t="s">
         <v>15</v>
@@ -4465,147 +4462,147 @@
         <v>21</v>
       </c>
       <c r="J63" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K63" t="s">
+        <v>204</v>
+      </c>
+      <c r="L63" t="s">
         <v>205</v>
       </c>
-      <c r="L63" t="s">
-        <v>206</v>
-      </c>
       <c r="M63" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B64" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D64" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E64" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F64" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G64" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H64" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I64" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J64" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K64" t="s">
+        <v>206</v>
+      </c>
+      <c r="L64" t="s">
         <v>207</v>
       </c>
-      <c r="L64" t="s">
-        <v>208</v>
-      </c>
       <c r="M64" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B65" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C65" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D65" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E65" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F65" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G65" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H65" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I65" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J65" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K65" t="s">
+        <v>208</v>
+      </c>
+      <c r="L65" t="s">
         <v>209</v>
       </c>
-      <c r="L65" t="s">
-        <v>210</v>
-      </c>
       <c r="M65" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B66" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C66" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D66" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E66" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F66" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G66" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H66" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I66" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J66" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K66" t="s">
+        <v>210</v>
+      </c>
+      <c r="L66" t="s">
         <v>211</v>
       </c>
-      <c r="L66" t="s">
-        <v>212</v>
-      </c>
       <c r="M66" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>212</v>
+      </c>
+      <c r="B67" t="s">
         <v>213</v>
-      </c>
-      <c r="B67" t="s">
-        <v>214</v>
       </c>
       <c r="C67" t="s">
         <v>15</v>
@@ -4614,7 +4611,7 @@
         <v>16</v>
       </c>
       <c r="E67" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F67" t="s">
         <v>18</v>
@@ -4629,147 +4626,147 @@
         <v>21</v>
       </c>
       <c r="J67" t="s">
+        <v>214</v>
+      </c>
+      <c r="K67" t="s">
         <v>215</v>
       </c>
-      <c r="K67" t="s">
+      <c r="L67" t="s">
         <v>216</v>
       </c>
-      <c r="L67" t="s">
-        <v>217</v>
-      </c>
       <c r="M67" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B68" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C68" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D68" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E68" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F68" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G68" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H68" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I68" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J68" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K68" t="s">
+        <v>217</v>
+      </c>
+      <c r="L68" t="s">
         <v>218</v>
       </c>
-      <c r="L68" t="s">
-        <v>219</v>
-      </c>
       <c r="M68" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B69" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C69" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D69" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E69" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F69" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G69" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H69" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I69" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J69" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K69" t="s">
+        <v>219</v>
+      </c>
+      <c r="L69" t="s">
         <v>220</v>
       </c>
-      <c r="L69" t="s">
-        <v>221</v>
-      </c>
       <c r="M69" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B70" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C70" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D70" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E70" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F70" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G70" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H70" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I70" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J70" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K70" t="s">
+        <v>221</v>
+      </c>
+      <c r="L70" t="s">
         <v>222</v>
       </c>
-      <c r="L70" t="s">
-        <v>223</v>
-      </c>
       <c r="M70" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>223</v>
+      </c>
+      <c r="B71" t="s">
         <v>224</v>
-      </c>
-      <c r="B71" t="s">
-        <v>225</v>
       </c>
       <c r="C71" t="s">
         <v>15</v>
@@ -4778,7 +4775,7 @@
         <v>16</v>
       </c>
       <c r="E71" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F71" t="s">
         <v>18</v>
@@ -4793,147 +4790,147 @@
         <v>21</v>
       </c>
       <c r="J71" t="s">
+        <v>226</v>
+      </c>
+      <c r="K71" t="s">
         <v>227</v>
       </c>
-      <c r="K71" t="s">
+      <c r="L71" t="s">
         <v>228</v>
       </c>
-      <c r="L71" t="s">
-        <v>229</v>
-      </c>
       <c r="M71" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B72" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C72" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D72" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E72" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F72" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G72" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H72" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I72" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J72" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K72" t="s">
+        <v>229</v>
+      </c>
+      <c r="L72" t="s">
         <v>230</v>
       </c>
-      <c r="L72" t="s">
-        <v>231</v>
-      </c>
       <c r="M72" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B73" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C73" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D73" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E73" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F73" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G73" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H73" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I73" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J73" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K73" t="s">
+        <v>231</v>
+      </c>
+      <c r="L73" t="s">
         <v>232</v>
       </c>
-      <c r="L73" t="s">
-        <v>233</v>
-      </c>
       <c r="M73" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B74" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C74" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D74" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E74" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F74" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G74" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H74" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I74" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J74" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K74" t="s">
+        <v>233</v>
+      </c>
+      <c r="L74" t="s">
         <v>234</v>
       </c>
-      <c r="L74" t="s">
-        <v>235</v>
-      </c>
       <c r="M74" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>235</v>
+      </c>
+      <c r="B75" t="s">
         <v>236</v>
-      </c>
-      <c r="B75" t="s">
-        <v>237</v>
       </c>
       <c r="C75" t="s">
         <v>15</v>
@@ -4942,7 +4939,7 @@
         <v>16</v>
       </c>
       <c r="E75" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F75" t="s">
         <v>18</v>
@@ -4957,147 +4954,147 @@
         <v>21</v>
       </c>
       <c r="J75" t="s">
+        <v>238</v>
+      </c>
+      <c r="K75" t="s">
         <v>239</v>
       </c>
-      <c r="K75" t="s">
+      <c r="L75" t="s">
         <v>240</v>
       </c>
-      <c r="L75" t="s">
-        <v>241</v>
-      </c>
       <c r="M75" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B76" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C76" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D76" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E76" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F76" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G76" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H76" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I76" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J76" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K76" t="s">
+        <v>241</v>
+      </c>
+      <c r="L76" t="s">
         <v>242</v>
       </c>
-      <c r="L76" t="s">
-        <v>243</v>
-      </c>
       <c r="M76" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B77" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C77" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D77" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E77" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F77" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G77" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H77" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I77" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J77" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K77" t="s">
+        <v>243</v>
+      </c>
+      <c r="L77" t="s">
         <v>244</v>
       </c>
-      <c r="L77" t="s">
-        <v>245</v>
-      </c>
       <c r="M77" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B78" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C78" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D78" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E78" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F78" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G78" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H78" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I78" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J78" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K78" t="s">
+        <v>245</v>
+      </c>
+      <c r="L78" t="s">
         <v>246</v>
       </c>
-      <c r="L78" t="s">
-        <v>247</v>
-      </c>
       <c r="M78" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>247</v>
+      </c>
+      <c r="B79" t="s">
         <v>248</v>
-      </c>
-      <c r="B79" t="s">
-        <v>249</v>
       </c>
       <c r="C79" t="s">
         <v>15</v>
@@ -5106,7 +5103,7 @@
         <v>16</v>
       </c>
       <c r="E79" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F79" t="s">
         <v>18</v>
@@ -5121,147 +5118,147 @@
         <v>21</v>
       </c>
       <c r="J79" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K79" t="s">
+        <v>250</v>
+      </c>
+      <c r="L79" t="s">
         <v>251</v>
       </c>
-      <c r="L79" t="s">
-        <v>252</v>
-      </c>
       <c r="M79" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B80" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C80" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D80" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E80" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F80" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G80" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H80" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I80" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J80" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K80" t="s">
+        <v>252</v>
+      </c>
+      <c r="L80" t="s">
         <v>253</v>
       </c>
-      <c r="L80" t="s">
-        <v>254</v>
-      </c>
       <c r="M80" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B81" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C81" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D81" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E81" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F81" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G81" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H81" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I81" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J81" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K81" t="s">
+        <v>254</v>
+      </c>
+      <c r="L81" t="s">
         <v>255</v>
       </c>
-      <c r="L81" t="s">
-        <v>256</v>
-      </c>
       <c r="M81" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B82" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C82" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D82" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E82" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F82" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G82" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H82" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I82" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J82" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K82" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L82" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M82" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>256</v>
+      </c>
+      <c r="B83" t="s">
         <v>257</v>
-      </c>
-      <c r="B83" t="s">
-        <v>258</v>
       </c>
       <c r="C83" t="s">
         <v>15</v>
@@ -5285,106 +5282,106 @@
         <v>21</v>
       </c>
       <c r="J83" t="s">
+        <v>258</v>
+      </c>
+      <c r="K83" t="s">
         <v>259</v>
       </c>
-      <c r="K83" t="s">
+      <c r="L83" t="s">
         <v>260</v>
       </c>
-      <c r="L83" t="s">
-        <v>261</v>
-      </c>
       <c r="M83" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B84" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C84" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D84" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E84" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F84" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G84" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H84" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I84" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J84" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K84" t="s">
+        <v>261</v>
+      </c>
+      <c r="L84" t="s">
         <v>262</v>
       </c>
-      <c r="L84" t="s">
-        <v>263</v>
-      </c>
       <c r="M84" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B85" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C85" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D85" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E85" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F85" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G85" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H85" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I85" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J85" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K85" t="s">
+        <v>263</v>
+      </c>
+      <c r="L85" t="s">
         <v>264</v>
       </c>
-      <c r="L85" t="s">
-        <v>265</v>
-      </c>
       <c r="M85" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>265</v>
+      </c>
+      <c r="B86" t="s">
         <v>266</v>
-      </c>
-      <c r="B86" t="s">
-        <v>267</v>
       </c>
       <c r="C86" t="s">
         <v>15</v>
@@ -5393,7 +5390,7 @@
         <v>16</v>
       </c>
       <c r="E86" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F86" t="s">
         <v>18</v>
@@ -5408,65 +5405,65 @@
         <v>21</v>
       </c>
       <c r="J86" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K86" t="s">
+        <v>268</v>
+      </c>
+      <c r="L86" t="s">
         <v>269</v>
       </c>
-      <c r="L86" t="s">
-        <v>270</v>
-      </c>
       <c r="M86" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B87" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C87" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D87" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E87" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F87" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G87" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H87" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I87" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J87" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K87" t="s">
+        <v>270</v>
+      </c>
+      <c r="L87" t="s">
         <v>271</v>
       </c>
-      <c r="L87" t="s">
-        <v>272</v>
-      </c>
       <c r="M87" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>272</v>
+      </c>
+      <c r="B88" t="s">
         <v>273</v>
-      </c>
-      <c r="B88" t="s">
-        <v>274</v>
       </c>
       <c r="C88" t="s">
         <v>15</v>
@@ -5490,24 +5487,24 @@
         <v>21</v>
       </c>
       <c r="J88" t="s">
+        <v>274</v>
+      </c>
+      <c r="K88" t="s">
         <v>275</v>
       </c>
-      <c r="K88" t="s">
+      <c r="L88" t="s">
         <v>276</v>
       </c>
-      <c r="L88" t="s">
-        <v>277</v>
-      </c>
       <c r="M88" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>277</v>
+      </c>
+      <c r="B89" t="s">
         <v>278</v>
-      </c>
-      <c r="B89" t="s">
-        <v>279</v>
       </c>
       <c r="C89" t="s">
         <v>15</v>
@@ -5516,7 +5513,7 @@
         <v>16</v>
       </c>
       <c r="E89" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F89" t="s">
         <v>18</v>
@@ -5531,147 +5528,147 @@
         <v>21</v>
       </c>
       <c r="J89" t="s">
+        <v>280</v>
+      </c>
+      <c r="K89" t="s">
         <v>281</v>
       </c>
-      <c r="K89" t="s">
+      <c r="L89" t="s">
         <v>282</v>
       </c>
-      <c r="L89" t="s">
-        <v>283</v>
-      </c>
       <c r="M89" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B90" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C90" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D90" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E90" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F90" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G90" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H90" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I90" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J90" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K90" t="s">
+        <v>283</v>
+      </c>
+      <c r="L90" t="s">
         <v>284</v>
       </c>
-      <c r="L90" t="s">
-        <v>285</v>
-      </c>
       <c r="M90" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B91" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C91" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D91" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E91" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F91" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G91" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H91" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I91" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J91" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K91" t="s">
+        <v>285</v>
+      </c>
+      <c r="L91" t="s">
         <v>286</v>
       </c>
-      <c r="L91" t="s">
-        <v>287</v>
-      </c>
       <c r="M91" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B92" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C92" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D92" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E92" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F92" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G92" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H92" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I92" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J92" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K92" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L92" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M92" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>288</v>
+      </c>
+      <c r="B93" t="s">
         <v>289</v>
-      </c>
-      <c r="B93" t="s">
-        <v>290</v>
       </c>
       <c r="C93" t="s">
         <v>15</v>
@@ -5680,7 +5677,7 @@
         <v>16</v>
       </c>
       <c r="E93" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F93" t="s">
         <v>18</v>
@@ -5695,106 +5692,106 @@
         <v>21</v>
       </c>
       <c r="J93" t="s">
+        <v>238</v>
+      </c>
+      <c r="K93" t="s">
         <v>239</v>
       </c>
-      <c r="K93" t="s">
-        <v>240</v>
-      </c>
       <c r="L93" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M93" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B94" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C94" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D94" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E94" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F94" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G94" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H94" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I94" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J94" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K94" t="s">
+        <v>291</v>
+      </c>
+      <c r="L94" t="s">
         <v>292</v>
       </c>
-      <c r="L94" t="s">
-        <v>293</v>
-      </c>
       <c r="M94" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B95" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C95" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D95" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E95" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F95" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G95" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H95" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I95" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J95" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K95" t="s">
+        <v>293</v>
+      </c>
+      <c r="L95" t="s">
         <v>294</v>
       </c>
-      <c r="L95" t="s">
-        <v>295</v>
-      </c>
       <c r="M95" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>295</v>
+      </c>
+      <c r="B96" t="s">
         <v>296</v>
-      </c>
-      <c r="B96" t="s">
-        <v>297</v>
       </c>
       <c r="C96" t="s">
         <v>15</v>
@@ -5803,7 +5800,7 @@
         <v>16</v>
       </c>
       <c r="E96" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F96" t="s">
         <v>18</v>
@@ -5818,106 +5815,106 @@
         <v>21</v>
       </c>
       <c r="J96" t="s">
+        <v>298</v>
+      </c>
+      <c r="K96" t="s">
         <v>299</v>
       </c>
-      <c r="K96" t="s">
+      <c r="L96" t="s">
         <v>300</v>
       </c>
-      <c r="L96" t="s">
-        <v>301</v>
-      </c>
       <c r="M96" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B97" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C97" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D97" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E97" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F97" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G97" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H97" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I97" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J97" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K97" t="s">
+        <v>301</v>
+      </c>
+      <c r="L97" t="s">
         <v>302</v>
       </c>
-      <c r="L97" t="s">
-        <v>303</v>
-      </c>
       <c r="M97" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B98" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C98" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D98" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E98" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F98" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G98" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H98" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I98" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J98" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K98" t="s">
+        <v>303</v>
+      </c>
+      <c r="L98" t="s">
         <v>304</v>
       </c>
-      <c r="L98" t="s">
-        <v>305</v>
-      </c>
       <c r="M98" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>305</v>
+      </c>
+      <c r="B99" t="s">
         <v>306</v>
-      </c>
-      <c r="B99" t="s">
-        <v>307</v>
       </c>
       <c r="C99" t="s">
         <v>15</v>
@@ -5941,106 +5938,106 @@
         <v>21</v>
       </c>
       <c r="J99" t="s">
+        <v>163</v>
+      </c>
+      <c r="K99" t="s">
         <v>164</v>
       </c>
-      <c r="K99" t="s">
+      <c r="L99" t="s">
         <v>165</v>
       </c>
-      <c r="L99" t="s">
-        <v>166</v>
-      </c>
       <c r="M99" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B100" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C100" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D100" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E100" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F100" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G100" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H100" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I100" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J100" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K100" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L100" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="M100" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B101" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C101" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D101" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E101" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F101" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G101" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H101" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I101" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J101" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K101" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L101" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="M101" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>309</v>
+      </c>
+      <c r="B102" t="s">
         <v>310</v>
-      </c>
-      <c r="B102" t="s">
-        <v>311</v>
       </c>
       <c r="C102" t="s">
         <v>15</v>
@@ -6064,106 +6061,106 @@
         <v>21</v>
       </c>
       <c r="J102" t="s">
+        <v>163</v>
+      </c>
+      <c r="K102" t="s">
         <v>164</v>
       </c>
-      <c r="K102" t="s">
+      <c r="L102" t="s">
         <v>165</v>
       </c>
-      <c r="L102" t="s">
-        <v>166</v>
-      </c>
       <c r="M102" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B103" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C103" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D103" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E103" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F103" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G103" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H103" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I103" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J103" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K103" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L103" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M103" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B104" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C104" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D104" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E104" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F104" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G104" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H104" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I104" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J104" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K104" t="s">
+        <v>312</v>
+      </c>
+      <c r="L104" t="s">
         <v>313</v>
       </c>
-      <c r="L104" t="s">
-        <v>314</v>
-      </c>
       <c r="M104" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>314</v>
+      </c>
+      <c r="B105" t="s">
         <v>315</v>
-      </c>
-      <c r="B105" t="s">
-        <v>316</v>
       </c>
       <c r="C105" t="s">
         <v>15</v>
@@ -6187,106 +6184,106 @@
         <v>21</v>
       </c>
       <c r="J105" t="s">
+        <v>163</v>
+      </c>
+      <c r="K105" t="s">
         <v>164</v>
       </c>
-      <c r="K105" t="s">
+      <c r="L105" t="s">
         <v>165</v>
       </c>
-      <c r="L105" t="s">
-        <v>166</v>
-      </c>
       <c r="M105" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B106" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C106" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D106" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E106" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F106" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G106" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H106" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I106" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J106" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K106" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L106" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M106" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B107" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C107" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D107" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E107" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F107" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G107" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H107" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I107" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J107" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K107" t="s">
+        <v>317</v>
+      </c>
+      <c r="L107" t="s">
         <v>318</v>
       </c>
-      <c r="L107" t="s">
-        <v>319</v>
-      </c>
       <c r="M107" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>319</v>
+      </c>
+      <c r="B108" t="s">
         <v>320</v>
-      </c>
-      <c r="B108" t="s">
-        <v>321</v>
       </c>
       <c r="C108" t="s">
         <v>15</v>
@@ -6310,106 +6307,106 @@
         <v>21</v>
       </c>
       <c r="J108" t="s">
+        <v>163</v>
+      </c>
+      <c r="K108" t="s">
         <v>164</v>
       </c>
-      <c r="K108" t="s">
+      <c r="L108" t="s">
         <v>165</v>
       </c>
-      <c r="L108" t="s">
-        <v>166</v>
-      </c>
       <c r="M108" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B109" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C109" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D109" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E109" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F109" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G109" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H109" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I109" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J109" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K109" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L109" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M109" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B110" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C110" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D110" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E110" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F110" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G110" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H110" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I110" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J110" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K110" t="s">
+        <v>322</v>
+      </c>
+      <c r="L110" t="s">
         <v>323</v>
       </c>
-      <c r="L110" t="s">
-        <v>324</v>
-      </c>
       <c r="M110" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>324</v>
+      </c>
+      <c r="B111" t="s">
         <v>325</v>
-      </c>
-      <c r="B111" t="s">
-        <v>326</v>
       </c>
       <c r="C111" t="s">
         <v>15</v>
@@ -6418,7 +6415,7 @@
         <v>16</v>
       </c>
       <c r="E111" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F111" t="s">
         <v>18</v>
@@ -6433,147 +6430,147 @@
         <v>21</v>
       </c>
       <c r="J111" t="s">
+        <v>163</v>
+      </c>
+      <c r="K111" t="s">
         <v>164</v>
       </c>
-      <c r="K111" t="s">
+      <c r="L111" t="s">
         <v>165</v>
       </c>
-      <c r="L111" t="s">
-        <v>166</v>
-      </c>
       <c r="M111" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B112" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C112" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D112" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E112" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F112" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G112" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H112" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I112" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J112" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K112" t="s">
+        <v>327</v>
+      </c>
+      <c r="L112" t="s">
         <v>328</v>
       </c>
-      <c r="L112" t="s">
-        <v>329</v>
-      </c>
       <c r="M112" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B113" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C113" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D113" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E113" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F113" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G113" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H113" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I113" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J113" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K113" t="s">
+        <v>329</v>
+      </c>
+      <c r="L113" t="s">
         <v>330</v>
       </c>
-      <c r="L113" t="s">
-        <v>331</v>
-      </c>
       <c r="M113" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B114" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C114" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D114" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E114" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F114" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G114" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H114" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I114" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J114" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K114" t="s">
+        <v>331</v>
+      </c>
+      <c r="L114" t="s">
         <v>332</v>
       </c>
-      <c r="L114" t="s">
-        <v>333</v>
-      </c>
       <c r="M114" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>333</v>
+      </c>
+      <c r="B115" t="s">
         <v>334</v>
-      </c>
-      <c r="B115" t="s">
-        <v>335</v>
       </c>
       <c r="C115" t="s">
         <v>15</v>
@@ -6597,106 +6594,106 @@
         <v>21</v>
       </c>
       <c r="J115" t="s">
+        <v>163</v>
+      </c>
+      <c r="K115" t="s">
         <v>164</v>
       </c>
-      <c r="K115" t="s">
+      <c r="L115" t="s">
         <v>165</v>
       </c>
-      <c r="L115" t="s">
-        <v>166</v>
-      </c>
       <c r="M115" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B116" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C116" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D116" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E116" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F116" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G116" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H116" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I116" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J116" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K116" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L116" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M116" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B117" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C117" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D117" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E117" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F117" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G117" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H117" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I117" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J117" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K117" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L117" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M117" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>337</v>
+      </c>
+      <c r="B118" t="s">
         <v>338</v>
-      </c>
-      <c r="B118" t="s">
-        <v>339</v>
       </c>
       <c r="C118" t="s">
         <v>15</v>
@@ -6720,106 +6717,106 @@
         <v>21</v>
       </c>
       <c r="J118" t="s">
+        <v>163</v>
+      </c>
+      <c r="K118" t="s">
         <v>164</v>
       </c>
-      <c r="K118" t="s">
+      <c r="L118" t="s">
         <v>165</v>
       </c>
-      <c r="L118" t="s">
-        <v>166</v>
-      </c>
       <c r="M118" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B119" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C119" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D119" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E119" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F119" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G119" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H119" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I119" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J119" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K119" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L119" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M119" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B120" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C120" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D120" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E120" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F120" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G120" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H120" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I120" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J120" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K120" t="s">
+        <v>340</v>
+      </c>
+      <c r="L120" t="s">
         <v>341</v>
       </c>
-      <c r="L120" t="s">
-        <v>342</v>
-      </c>
       <c r="M120" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>342</v>
+      </c>
+      <c r="B121" t="s">
         <v>343</v>
-      </c>
-      <c r="B121" t="s">
-        <v>344</v>
       </c>
       <c r="C121" t="s">
         <v>15</v>
@@ -6843,106 +6840,106 @@
         <v>21</v>
       </c>
       <c r="J121" t="s">
+        <v>163</v>
+      </c>
+      <c r="K121" t="s">
         <v>164</v>
       </c>
-      <c r="K121" t="s">
+      <c r="L121" t="s">
         <v>165</v>
       </c>
-      <c r="L121" t="s">
-        <v>166</v>
-      </c>
       <c r="M121" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B122" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C122" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D122" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E122" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F122" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G122" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H122" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I122" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J122" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K122" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L122" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="M122" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B123" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C123" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D123" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E123" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F123" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G123" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H123" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I123" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J123" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K123" t="s">
+        <v>345</v>
+      </c>
+      <c r="L123" t="s">
         <v>346</v>
       </c>
-      <c r="L123" t="s">
-        <v>347</v>
-      </c>
       <c r="M123" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>347</v>
+      </c>
+      <c r="B124" t="s">
         <v>348</v>
-      </c>
-      <c r="B124" t="s">
-        <v>349</v>
       </c>
       <c r="C124" t="s">
         <v>15</v>
@@ -6966,106 +6963,106 @@
         <v>21</v>
       </c>
       <c r="J124" t="s">
+        <v>163</v>
+      </c>
+      <c r="K124" t="s">
         <v>164</v>
       </c>
-      <c r="K124" t="s">
+      <c r="L124" t="s">
         <v>165</v>
       </c>
-      <c r="L124" t="s">
-        <v>166</v>
-      </c>
       <c r="M124" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B125" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C125" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D125" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E125" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F125" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G125" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H125" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I125" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J125" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K125" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L125" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="M125" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B126" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C126" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D126" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E126" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F126" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G126" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H126" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I126" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J126" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K126" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L126" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M126" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>351</v>
+      </c>
+      <c r="B127" t="s">
         <v>352</v>
-      </c>
-      <c r="B127" t="s">
-        <v>353</v>
       </c>
       <c r="C127" t="s">
         <v>15</v>
@@ -7074,7 +7071,7 @@
         <v>16</v>
       </c>
       <c r="E127" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F127" t="s">
         <v>18</v>
@@ -7089,229 +7086,229 @@
         <v>21</v>
       </c>
       <c r="J127" t="s">
+        <v>163</v>
+      </c>
+      <c r="K127" t="s">
         <v>164</v>
       </c>
-      <c r="K127" t="s">
+      <c r="L127" t="s">
         <v>165</v>
       </c>
-      <c r="L127" t="s">
-        <v>166</v>
-      </c>
       <c r="M127" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B128" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C128" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D128" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E128" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F128" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G128" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H128" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I128" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J128" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K128" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L128" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="M128" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B129" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C129" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D129" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E129" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F129" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G129" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H129" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I129" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J129" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K129" t="s">
+        <v>355</v>
+      </c>
+      <c r="L129" t="s">
         <v>356</v>
       </c>
-      <c r="L129" t="s">
-        <v>357</v>
-      </c>
       <c r="M129" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B130" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C130" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D130" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E130" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F130" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G130" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H130" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I130" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J130" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K130" t="s">
+        <v>357</v>
+      </c>
+      <c r="L130" t="s">
         <v>358</v>
       </c>
-      <c r="L130" t="s">
-        <v>359</v>
-      </c>
       <c r="M130" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B131" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C131" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D131" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E131" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F131" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G131" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H131" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I131" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J131" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K131" t="s">
+        <v>359</v>
+      </c>
+      <c r="L131" t="s">
         <v>360</v>
       </c>
-      <c r="L131" t="s">
-        <v>361</v>
-      </c>
       <c r="M131" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B132" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C132" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D132" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E132" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F132" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G132" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H132" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I132" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J132" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K132" t="s">
+        <v>361</v>
+      </c>
+      <c r="L132" t="s">
         <v>362</v>
       </c>
-      <c r="L132" t="s">
-        <v>363</v>
-      </c>
       <c r="M132" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>363</v>
+      </c>
+      <c r="B133" t="s">
         <v>364</v>
-      </c>
-      <c r="B133" t="s">
-        <v>365</v>
       </c>
       <c r="C133" t="s">
         <v>15</v>
@@ -7335,106 +7332,106 @@
         <v>21</v>
       </c>
       <c r="J133" t="s">
+        <v>163</v>
+      </c>
+      <c r="K133" t="s">
         <v>164</v>
       </c>
-      <c r="K133" t="s">
+      <c r="L133" t="s">
         <v>165</v>
       </c>
-      <c r="L133" t="s">
-        <v>166</v>
-      </c>
       <c r="M133" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B134" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C134" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D134" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E134" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F134" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G134" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H134" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I134" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J134" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K134" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L134" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="M134" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B135" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C135" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D135" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E135" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F135" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G135" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H135" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I135" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J135" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K135" t="s">
+        <v>366</v>
+      </c>
+      <c r="L135" t="s">
         <v>367</v>
       </c>
-      <c r="L135" t="s">
-        <v>368</v>
-      </c>
       <c r="M135" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>368</v>
+      </c>
+      <c r="B136" t="s">
         <v>369</v>
-      </c>
-      <c r="B136" t="s">
-        <v>370</v>
       </c>
       <c r="C136" t="s">
         <v>15</v>
@@ -7458,106 +7455,106 @@
         <v>21</v>
       </c>
       <c r="J136" t="s">
+        <v>163</v>
+      </c>
+      <c r="K136" t="s">
         <v>164</v>
       </c>
-      <c r="K136" t="s">
+      <c r="L136" t="s">
         <v>165</v>
       </c>
-      <c r="L136" t="s">
-        <v>166</v>
-      </c>
       <c r="M136" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B137" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C137" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D137" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E137" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F137" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G137" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H137" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I137" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J137" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K137" t="s">
+        <v>167</v>
+      </c>
+      <c r="L137" t="s">
         <v>168</v>
       </c>
-      <c r="L137" t="s">
-        <v>169</v>
-      </c>
       <c r="M137" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B138" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C138" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D138" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E138" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F138" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G138" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H138" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I138" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J138" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K138" t="s">
+        <v>169</v>
+      </c>
+      <c r="L138" t="s">
         <v>170</v>
       </c>
-      <c r="L138" t="s">
-        <v>171</v>
-      </c>
       <c r="M138" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>370</v>
+      </c>
+      <c r="B139" t="s">
         <v>371</v>
-      </c>
-      <c r="B139" t="s">
-        <v>372</v>
       </c>
       <c r="C139" t="s">
         <v>15</v>
@@ -7566,7 +7563,7 @@
         <v>16</v>
       </c>
       <c r="E139" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F139" t="s">
         <v>18</v>
@@ -7581,229 +7578,229 @@
         <v>21</v>
       </c>
       <c r="J139" t="s">
+        <v>163</v>
+      </c>
+      <c r="K139" t="s">
         <v>164</v>
       </c>
-      <c r="K139" t="s">
+      <c r="L139" t="s">
         <v>165</v>
       </c>
-      <c r="L139" t="s">
-        <v>166</v>
-      </c>
       <c r="M139" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B140" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C140" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D140" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E140" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F140" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G140" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H140" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I140" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J140" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K140" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L140" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M140" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B141" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C141" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D141" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E141" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F141" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G141" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H141" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I141" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J141" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K141" t="s">
+        <v>373</v>
+      </c>
+      <c r="L141" t="s">
         <v>374</v>
       </c>
-      <c r="L141" t="s">
-        <v>375</v>
-      </c>
       <c r="M141" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B142" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C142" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D142" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E142" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F142" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G142" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H142" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I142" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J142" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K142" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="L142" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="M142" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B143" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C143" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D143" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E143" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F143" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G143" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H143" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I143" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J143" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K143" t="s">
+        <v>376</v>
+      </c>
+      <c r="L143" t="s">
         <v>377</v>
       </c>
-      <c r="L143" t="s">
-        <v>378</v>
-      </c>
       <c r="M143" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B144" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C144" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D144" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E144" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F144" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G144" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H144" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I144" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J144" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K144" t="s">
+        <v>378</v>
+      </c>
+      <c r="L144" t="s">
         <v>379</v>
       </c>
-      <c r="L144" t="s">
-        <v>380</v>
-      </c>
       <c r="M144" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
+        <v>380</v>
+      </c>
+      <c r="B145" t="s">
         <v>381</v>
-      </c>
-      <c r="B145" t="s">
-        <v>382</v>
       </c>
       <c r="C145" t="s">
         <v>15</v>
@@ -7812,7 +7809,7 @@
         <v>16</v>
       </c>
       <c r="E145" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F145" t="s">
         <v>18</v>
@@ -7827,147 +7824,147 @@
         <v>21</v>
       </c>
       <c r="J145" t="s">
+        <v>163</v>
+      </c>
+      <c r="K145" t="s">
         <v>164</v>
       </c>
-      <c r="K145" t="s">
+      <c r="L145" t="s">
         <v>165</v>
       </c>
-      <c r="L145" t="s">
-        <v>166</v>
-      </c>
       <c r="M145" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B146" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C146" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D146" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E146" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F146" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G146" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H146" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I146" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J146" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K146" t="s">
+        <v>382</v>
+      </c>
+      <c r="L146" t="s">
         <v>383</v>
       </c>
-      <c r="L146" t="s">
-        <v>384</v>
-      </c>
       <c r="M146" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B147" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C147" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D147" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E147" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F147" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G147" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H147" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I147" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J147" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K147" t="s">
+        <v>384</v>
+      </c>
+      <c r="L147" t="s">
         <v>385</v>
       </c>
-      <c r="L147" t="s">
-        <v>386</v>
-      </c>
       <c r="M147" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B148" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C148" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D148" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E148" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F148" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G148" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H148" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I148" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J148" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K148" t="s">
+        <v>386</v>
+      </c>
+      <c r="L148" t="s">
         <v>387</v>
       </c>
-      <c r="L148" t="s">
-        <v>388</v>
-      </c>
       <c r="M148" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
+        <v>388</v>
+      </c>
+      <c r="B149" t="s">
         <v>389</v>
-      </c>
-      <c r="B149" t="s">
-        <v>390</v>
       </c>
       <c r="C149" t="s">
         <v>15</v>
@@ -7991,106 +7988,106 @@
         <v>21</v>
       </c>
       <c r="J149" t="s">
+        <v>163</v>
+      </c>
+      <c r="K149" t="s">
         <v>164</v>
       </c>
-      <c r="K149" t="s">
+      <c r="L149" t="s">
         <v>165</v>
       </c>
-      <c r="L149" t="s">
-        <v>166</v>
-      </c>
       <c r="M149" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B150" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C150" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D150" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E150" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F150" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G150" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H150" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I150" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J150" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K150" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L150" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="M150" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B151" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C151" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D151" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E151" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F151" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G151" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H151" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I151" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J151" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K151" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L151" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M151" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
+        <v>392</v>
+      </c>
+      <c r="B152" t="s">
         <v>393</v>
-      </c>
-      <c r="B152" t="s">
-        <v>394</v>
       </c>
       <c r="C152" t="s">
         <v>15</v>
@@ -8114,106 +8111,106 @@
         <v>21</v>
       </c>
       <c r="J152" t="s">
+        <v>163</v>
+      </c>
+      <c r="K152" t="s">
         <v>164</v>
       </c>
-      <c r="K152" t="s">
+      <c r="L152" t="s">
         <v>165</v>
       </c>
-      <c r="L152" t="s">
-        <v>166</v>
-      </c>
       <c r="M152" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B153" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C153" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D153" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E153" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F153" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G153" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H153" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I153" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J153" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K153" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L153" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="M153" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B154" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C154" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D154" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E154" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F154" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G154" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H154" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I154" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J154" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K154" t="s">
+        <v>395</v>
+      </c>
+      <c r="L154" t="s">
         <v>396</v>
       </c>
-      <c r="L154" t="s">
-        <v>397</v>
-      </c>
       <c r="M154" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
+        <v>397</v>
+      </c>
+      <c r="B155" t="s">
         <v>398</v>
-      </c>
-      <c r="B155" t="s">
-        <v>399</v>
       </c>
       <c r="C155" t="s">
         <v>15</v>
@@ -8237,106 +8234,106 @@
         <v>21</v>
       </c>
       <c r="J155" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K155" t="s">
+        <v>164</v>
+      </c>
+      <c r="L155" t="s">
         <v>165</v>
       </c>
-      <c r="L155" t="s">
-        <v>166</v>
-      </c>
       <c r="M155" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B156" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C156" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D156" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E156" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F156" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G156" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H156" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I156" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J156" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K156" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L156" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="M156" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B157" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C157" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D157" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E157" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F157" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G157" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H157" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I157" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J157" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K157" t="s">
+        <v>401</v>
+      </c>
+      <c r="L157" t="s">
         <v>402</v>
       </c>
-      <c r="L157" t="s">
-        <v>403</v>
-      </c>
       <c r="M157" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>403</v>
+      </c>
+      <c r="B158" t="s">
         <v>404</v>
-      </c>
-      <c r="B158" t="s">
-        <v>405</v>
       </c>
       <c r="C158" t="s">
         <v>15</v>
@@ -8360,106 +8357,106 @@
         <v>21</v>
       </c>
       <c r="J158" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K158" t="s">
+        <v>164</v>
+      </c>
+      <c r="L158" t="s">
         <v>165</v>
       </c>
-      <c r="L158" t="s">
-        <v>166</v>
-      </c>
       <c r="M158" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B159" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C159" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D159" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E159" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F159" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G159" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H159" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I159" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J159" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K159" t="s">
+        <v>406</v>
+      </c>
+      <c r="L159" t="s">
         <v>407</v>
       </c>
-      <c r="L159" t="s">
-        <v>408</v>
-      </c>
       <c r="M159" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B160" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C160" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D160" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E160" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F160" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G160" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H160" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I160" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J160" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K160" t="s">
+        <v>408</v>
+      </c>
+      <c r="L160" t="s">
         <v>409</v>
       </c>
-      <c r="L160" t="s">
-        <v>410</v>
-      </c>
       <c r="M160" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>410</v>
+      </c>
+      <c r="B161" t="s">
         <v>411</v>
-      </c>
-      <c r="B161" t="s">
-        <v>412</v>
       </c>
       <c r="C161" t="s">
         <v>15</v>
@@ -8468,7 +8465,7 @@
         <v>16</v>
       </c>
       <c r="E161" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F161" t="s">
         <v>18</v>
@@ -8480,232 +8477,232 @@
         <v>20</v>
       </c>
       <c r="I161" t="s">
+        <v>412</v>
+      </c>
+      <c r="J161" t="s">
         <v>413</v>
       </c>
-      <c r="J161" t="s">
+      <c r="K161" t="s">
         <v>414</v>
       </c>
-      <c r="K161" t="s">
+      <c r="L161" t="s">
         <v>415</v>
       </c>
-      <c r="L161" t="s">
-        <v>416</v>
-      </c>
       <c r="M161" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B162" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C162" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D162" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E162" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F162" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G162" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H162" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I162" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J162" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K162" t="s">
+        <v>416</v>
+      </c>
+      <c r="L162" t="s">
         <v>417</v>
       </c>
-      <c r="L162" t="s">
-        <v>418</v>
-      </c>
       <c r="M162" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B163" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C163" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D163" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E163" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F163" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G163" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H163" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I163" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J163" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K163" t="s">
+        <v>418</v>
+      </c>
+      <c r="L163" t="s">
         <v>419</v>
       </c>
-      <c r="L163" t="s">
-        <v>420</v>
-      </c>
       <c r="M163" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B164" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C164" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D164" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E164" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F164" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G164" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H164" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I164" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J164" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K164" t="s">
+        <v>420</v>
+      </c>
+      <c r="L164" t="s">
         <v>421</v>
       </c>
-      <c r="L164" t="s">
-        <v>422</v>
-      </c>
       <c r="M164" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B165" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C165" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D165" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E165" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F165" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G165" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H165" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I165" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J165" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K165" t="s">
+        <v>422</v>
+      </c>
+      <c r="L165" t="s">
         <v>423</v>
       </c>
-      <c r="L165" t="s">
-        <v>424</v>
-      </c>
       <c r="M165" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B166" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C166" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D166" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E166" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F166" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G166" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H166" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I166" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J166" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K166" t="s">
+        <v>424</v>
+      </c>
+      <c r="L166" t="s">
         <v>425</v>
       </c>
-      <c r="L166" t="s">
-        <v>426</v>
-      </c>
       <c r="M166" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>426</v>
+      </c>
+      <c r="B167" t="s">
         <v>427</v>
-      </c>
-      <c r="B167" t="s">
-        <v>428</v>
       </c>
       <c r="C167" t="s">
         <v>15</v>
@@ -8729,229 +8726,229 @@
         <v>21</v>
       </c>
       <c r="J167" t="s">
+        <v>428</v>
+      </c>
+      <c r="K167" t="s">
         <v>429</v>
       </c>
-      <c r="K167" t="s">
-        <v>430</v>
-      </c>
       <c r="L167" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M167" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B168" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C168" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D168" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E168" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F168" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G168" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H168" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I168" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J168" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K168" t="s">
+        <v>430</v>
+      </c>
+      <c r="L168" t="s">
         <v>431</v>
       </c>
-      <c r="L168" t="s">
-        <v>432</v>
-      </c>
       <c r="M168" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B169" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C169" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D169" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E169" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F169" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G169" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H169" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I169" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J169" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K169" t="s">
+        <v>432</v>
+      </c>
+      <c r="L169" t="s">
         <v>433</v>
       </c>
-      <c r="L169" t="s">
-        <v>434</v>
-      </c>
       <c r="M169" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B170" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C170" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D170" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E170" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F170" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G170" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H170" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I170" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J170" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K170" t="s">
+        <v>434</v>
+      </c>
+      <c r="L170" t="s">
         <v>435</v>
       </c>
-      <c r="L170" t="s">
-        <v>436</v>
-      </c>
       <c r="M170" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B171" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C171" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D171" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E171" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F171" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G171" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H171" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I171" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J171" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K171" t="s">
+        <v>436</v>
+      </c>
+      <c r="L171" t="s">
         <v>437</v>
       </c>
-      <c r="L171" t="s">
-        <v>438</v>
-      </c>
       <c r="M171" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B172" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C172" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D172" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E172" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F172" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G172" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H172" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I172" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J172" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K172" t="s">
+        <v>438</v>
+      </c>
+      <c r="L172" t="s">
         <v>439</v>
       </c>
-      <c r="L172" t="s">
-        <v>440</v>
-      </c>
       <c r="M172" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
+        <v>440</v>
+      </c>
+      <c r="B173" t="s">
         <v>441</v>
-      </c>
-      <c r="B173" t="s">
-        <v>442</v>
       </c>
       <c r="C173" t="s">
         <v>15</v>
@@ -8975,188 +8972,188 @@
         <v>21</v>
       </c>
       <c r="J173" t="s">
+        <v>442</v>
+      </c>
+      <c r="K173" t="s">
         <v>443</v>
       </c>
-      <c r="K173" t="s">
-        <v>444</v>
-      </c>
       <c r="L173" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M173" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B174" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C174" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D174" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E174" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F174" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G174" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H174" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I174" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J174" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K174" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L174" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="M174" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B175" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C175" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D175" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E175" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F175" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G175" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H175" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I175" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J175" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K175" t="s">
+        <v>445</v>
+      </c>
+      <c r="L175" t="s">
         <v>446</v>
       </c>
-      <c r="L175" t="s">
-        <v>447</v>
-      </c>
       <c r="M175" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B176" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C176" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D176" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E176" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F176" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G176" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H176" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I176" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J176" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K176" t="s">
+        <v>447</v>
+      </c>
+      <c r="L176" t="s">
         <v>448</v>
       </c>
-      <c r="L176" t="s">
-        <v>449</v>
-      </c>
       <c r="M176" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B177" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C177" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D177" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E177" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F177" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G177" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H177" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I177" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J177" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K177" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L177" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="M177" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="178" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>450</v>
+      </c>
+      <c r="B178" t="s">
         <v>451</v>
-      </c>
-      <c r="B178" t="s">
-        <v>452</v>
       </c>
       <c r="C178" t="s">
         <v>15</v>
@@ -9180,106 +9177,106 @@
         <v>21</v>
       </c>
       <c r="J178" t="s">
+        <v>452</v>
+      </c>
+      <c r="K178" t="s">
         <v>453</v>
       </c>
-      <c r="K178" t="s">
+      <c r="L178" t="s">
         <v>454</v>
       </c>
-      <c r="L178" t="s">
-        <v>455</v>
-      </c>
       <c r="M178" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B179" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C179" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D179" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E179" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F179" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G179" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H179" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I179" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J179" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K179" t="s">
+        <v>455</v>
+      </c>
+      <c r="L179" t="s">
         <v>456</v>
       </c>
-      <c r="L179" t="s">
-        <v>457</v>
-      </c>
       <c r="M179" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B180" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C180" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D180" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E180" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F180" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G180" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H180" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I180" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J180" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K180" t="s">
+        <v>457</v>
+      </c>
+      <c r="L180" t="s">
         <v>458</v>
       </c>
-      <c r="L180" t="s">
-        <v>459</v>
-      </c>
       <c r="M180" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>459</v>
+      </c>
+      <c r="B181" t="s">
         <v>460</v>
-      </c>
-      <c r="B181" t="s">
-        <v>461</v>
       </c>
       <c r="C181" t="s">
         <v>15</v>
@@ -9303,221 +9300,221 @@
         <v>21</v>
       </c>
       <c r="J181" t="s">
+        <v>461</v>
+      </c>
+      <c r="K181" t="s">
         <v>462</v>
       </c>
-      <c r="K181" t="s">
+      <c r="L181" t="s">
         <v>463</v>
       </c>
-      <c r="L181" t="s">
-        <v>464</v>
-      </c>
       <c r="M181" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="182" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B182" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C182" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D182" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E182" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F182" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G182" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H182" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I182" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J182" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K182" t="s">
+        <v>464</v>
+      </c>
+      <c r="L182" t="s">
         <v>465</v>
       </c>
-      <c r="L182" t="s">
-        <v>466</v>
-      </c>
       <c r="M182" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B183" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C183" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D183" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E183" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F183" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G183" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H183" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I183" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J183" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K183" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="L183" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="M183" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B184" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C184" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D184" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E184" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F184" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G184" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H184" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I184" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J184" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K184" t="s">
+        <v>467</v>
+      </c>
+      <c r="L184" t="s">
         <v>468</v>
       </c>
-      <c r="L184" t="s">
-        <v>469</v>
-      </c>
       <c r="M184" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B185" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C185" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D185" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E185" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F185" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G185" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H185" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I185" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J185" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K185" t="s">
+        <v>469</v>
+      </c>
+      <c r="L185" t="s">
         <v>470</v>
       </c>
-      <c r="L185" t="s">
-        <v>471</v>
-      </c>
       <c r="M185" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B187" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="B187" s="2" t="s">
+      <c r="C187" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H187" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="C187" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D187" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E187" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F187" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G187" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H187" s="2" t="s">
+      <c r="I187" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="I187" s="2" t="s">
+      <c r="J187" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K187" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L187" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M187" s="2" t="s">
         <v>475</v>
-      </c>
-      <c r="J187" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K187" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L187" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M187" s="2" t="s">
-        <v>476</v>
       </c>
     </row>
   </sheetData>

--- a/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
@@ -5,13 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="corporate_override_core" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="__fp__" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2418" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2419" uniqueCount="478">
   <si>
     <t>TC ID</t>
   </si>
@@ -78,16 +79,19 @@
     <t>Automated</t>
   </si>
   <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Authenticated on office 1604</t>
+  </si>
+  <si>
+    <t>1. Navigate to the Product Group Override screen</t>
+  </si>
+  <si>
+    <t>The Product Group Override screen loads and is displayed.</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>Authenticated on office 1604</t>
-  </si>
-  <si>
-    <t>1. Navigate to the Product Group Override screen</t>
-  </si>
-  <si>
-    <t>The Product Group Override screen loads and is displayed.</t>
   </si>
   <si>
     <t>2. Read the active tab</t>
@@ -1485,10 +1489,13 @@
     <t>Automated: 61 / Pending: 0</t>
   </si>
   <si>
-    <t>Not run in this delivery</t>
-  </si>
-  <si>
-    <t>Last Updated: 2026-08-07</t>
+    <t>Pass:59 Fail:0 Skipped:1 Blocked:1</t>
+  </si>
+  <si>
+    <t>Last Updated: 2026-07-31</t>
+  </si>
+  <si>
+    <t>18ff78cd3fbd5f1eaea8671aab16ad4934208919e92d0cf838fb3049b31c1e53</t>
   </si>
 </sst>
 </file>
@@ -1887,7 +1894,7 @@
     <col min="5" max="5" width="80" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="9" max="9" width="36" customWidth="1"/>
     <col min="10" max="13" width="80" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1970,56 +1977,56 @@
         <v>24</v>
       </c>
       <c r="M2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -2043,65 +2050,65 @@
         <v>21</v>
       </c>
       <c r="J4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
@@ -2110,7 +2117,7 @@
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -2125,106 +2132,106 @@
         <v>21</v>
       </c>
       <c r="J6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
@@ -2233,7 +2240,7 @@
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -2248,106 +2255,106 @@
         <v>21</v>
       </c>
       <c r="J9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
         <v>15</v>
@@ -2371,24 +2378,24 @@
         <v>21</v>
       </c>
       <c r="J12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
         <v>15</v>
@@ -2412,24 +2419,24 @@
         <v>21</v>
       </c>
       <c r="J13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M13" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -2453,24 +2460,24 @@
         <v>21</v>
       </c>
       <c r="J14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
         <v>15</v>
@@ -2494,106 +2501,106 @@
         <v>21</v>
       </c>
       <c r="J15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
         <v>15</v>
@@ -2617,65 +2624,65 @@
         <v>21</v>
       </c>
       <c r="J18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M18" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
         <v>15</v>
@@ -2699,106 +2706,106 @@
         <v>21</v>
       </c>
       <c r="J20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M20" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
         <v>15</v>
@@ -2822,65 +2829,65 @@
         <v>21</v>
       </c>
       <c r="J23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M23" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
         <v>15</v>
@@ -2889,7 +2896,7 @@
         <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
@@ -2904,106 +2911,106 @@
         <v>21</v>
       </c>
       <c r="J25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M25" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s">
         <v>15</v>
@@ -3012,7 +3019,7 @@
         <v>16</v>
       </c>
       <c r="E28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F28" t="s">
         <v>18</v>
@@ -3027,106 +3034,106 @@
         <v>21</v>
       </c>
       <c r="J28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M28" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C29" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E29" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F29" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G29" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H29" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I29" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J29" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K29" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M29" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C31" t="s">
         <v>15</v>
@@ -3135,7 +3142,7 @@
         <v>16</v>
       </c>
       <c r="E31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F31" t="s">
         <v>18</v>
@@ -3150,65 +3157,65 @@
         <v>21</v>
       </c>
       <c r="J31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M31" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C33" t="s">
         <v>15</v>
@@ -3232,65 +3239,65 @@
         <v>21</v>
       </c>
       <c r="J33" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M33" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K34" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C35" t="s">
         <v>15</v>
@@ -3314,65 +3321,65 @@
         <v>21</v>
       </c>
       <c r="J35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K35" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M35" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K36" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L36" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B37" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C37" t="s">
         <v>15</v>
@@ -3396,65 +3403,65 @@
         <v>21</v>
       </c>
       <c r="J37" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K37" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L37" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M37" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K38" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L38" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B39" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C39" t="s">
         <v>15</v>
@@ -3478,65 +3485,65 @@
         <v>21</v>
       </c>
       <c r="J39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K39" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L39" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M39" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K40" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L40" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C41" t="s">
         <v>15</v>
@@ -3560,65 +3567,65 @@
         <v>21</v>
       </c>
       <c r="J41" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K41" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L41" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M41" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K42" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L42" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B43" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C43" t="s">
         <v>15</v>
@@ -3642,65 +3649,65 @@
         <v>21</v>
       </c>
       <c r="J43" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L43" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M43" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K44" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L44" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B45" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C45" t="s">
         <v>15</v>
@@ -3724,65 +3731,65 @@
         <v>21</v>
       </c>
       <c r="J45" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K45" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L45" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M45" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C46" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E46" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F46" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G46" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H46" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I46" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J46" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K46" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L46" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M46" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B47" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C47" t="s">
         <v>15</v>
@@ -3791,7 +3798,7 @@
         <v>16</v>
       </c>
       <c r="E47" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F47" t="s">
         <v>18</v>
@@ -3806,24 +3813,24 @@
         <v>21</v>
       </c>
       <c r="J47" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K47" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L47" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M47" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B48" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C48" t="s">
         <v>15</v>
@@ -3844,109 +3851,109 @@
         <v>20</v>
       </c>
       <c r="I48" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J48" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K48" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L48" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K49" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L49" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C50" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E50" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F50" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G50" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H50" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I50" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J50" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K50" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L50" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M50" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B51" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C51" t="s">
         <v>15</v>
@@ -3970,65 +3977,65 @@
         <v>21</v>
       </c>
       <c r="J51" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K51" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L51" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M51" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C52" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E52" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F52" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G52" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H52" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I52" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J52" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K52" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L52" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M52" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B53" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C53" t="s">
         <v>15</v>
@@ -4052,147 +4059,147 @@
         <v>21</v>
       </c>
       <c r="J53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K53" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L53" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M53" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C54" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D54" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E54" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F54" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G54" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H54" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I54" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J54" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K54" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L54" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M54" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C55" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D55" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E55" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F55" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G55" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H55" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I55" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J55" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K55" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L55" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M55" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C56" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D56" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E56" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F56" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G56" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H56" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I56" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J56" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K56" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L56" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M56" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B57" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C57" t="s">
         <v>15</v>
@@ -4216,106 +4223,106 @@
         <v>21</v>
       </c>
       <c r="J57" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K57" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L57" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M57" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C58" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D58" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E58" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F58" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G58" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H58" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I58" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J58" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K58" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L58" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M58" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C59" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D59" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E59" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F59" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G59" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H59" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I59" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J59" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K59" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L59" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M59" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B60" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C60" t="s">
         <v>15</v>
@@ -4339,106 +4346,106 @@
         <v>21</v>
       </c>
       <c r="J60" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K60" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L60" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M60" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B61" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C61" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E61" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F61" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G61" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H61" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I61" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J61" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K61" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L61" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M61" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B62" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C62" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D62" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E62" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F62" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G62" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H62" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I62" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J62" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K62" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L62" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M62" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B63" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C63" t="s">
         <v>15</v>
@@ -4462,147 +4469,147 @@
         <v>21</v>
       </c>
       <c r="J63" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K63" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L63" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M63" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C64" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D64" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E64" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F64" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G64" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H64" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I64" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J64" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K64" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L64" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M64" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B65" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C65" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D65" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E65" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F65" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G65" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H65" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I65" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J65" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K65" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M65" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B66" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C66" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D66" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E66" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F66" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G66" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H66" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I66" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J66" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L66" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M66" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B67" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C67" t="s">
         <v>15</v>
@@ -4611,7 +4618,7 @@
         <v>16</v>
       </c>
       <c r="E67" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F67" t="s">
         <v>18</v>
@@ -4626,147 +4633,147 @@
         <v>21</v>
       </c>
       <c r="J67" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K67" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L67" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M67" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B68" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C68" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D68" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E68" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F68" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G68" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H68" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I68" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J68" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K68" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L68" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M68" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C69" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D69" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E69" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F69" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G69" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H69" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I69" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J69" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K69" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L69" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M69" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B70" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C70" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D70" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E70" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F70" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G70" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H70" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I70" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J70" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K70" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L70" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M70" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B71" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C71" t="s">
         <v>15</v>
@@ -4775,7 +4782,7 @@
         <v>16</v>
       </c>
       <c r="E71" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F71" t="s">
         <v>18</v>
@@ -4790,147 +4797,147 @@
         <v>21</v>
       </c>
       <c r="J71" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K71" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L71" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M71" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B72" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C72" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D72" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E72" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F72" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G72" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H72" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I72" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J72" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K72" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L72" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M72" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B73" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C73" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D73" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E73" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F73" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G73" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H73" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I73" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J73" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K73" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L73" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M73" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B74" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C74" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D74" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E74" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F74" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G74" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H74" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I74" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J74" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K74" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L74" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M74" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B75" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C75" t="s">
         <v>15</v>
@@ -4939,7 +4946,7 @@
         <v>16</v>
       </c>
       <c r="E75" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F75" t="s">
         <v>18</v>
@@ -4954,147 +4961,147 @@
         <v>21</v>
       </c>
       <c r="J75" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K75" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L75" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M75" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B76" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C76" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D76" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E76" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F76" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G76" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H76" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I76" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J76" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K76" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L76" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M76" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B77" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C77" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D77" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E77" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F77" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G77" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H77" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I77" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J77" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K77" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L77" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M77" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B78" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C78" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E78" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F78" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G78" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H78" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I78" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J78" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K78" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L78" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M78" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B79" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C79" t="s">
         <v>15</v>
@@ -5103,7 +5110,7 @@
         <v>16</v>
       </c>
       <c r="E79" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F79" t="s">
         <v>18</v>
@@ -5118,147 +5125,147 @@
         <v>21</v>
       </c>
       <c r="J79" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K79" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L79" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M79" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B80" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C80" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D80" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E80" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F80" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G80" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H80" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I80" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J80" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K80" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L80" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M80" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B81" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C81" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D81" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E81" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F81" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G81" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H81" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I81" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J81" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K81" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L81" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M81" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B82" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C82" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D82" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E82" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F82" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G82" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H82" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I82" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J82" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K82" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L82" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M82" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B83" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C83" t="s">
         <v>15</v>
@@ -5282,106 +5289,106 @@
         <v>21</v>
       </c>
       <c r="J83" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K83" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L83" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M83" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B84" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C84" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D84" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E84" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F84" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G84" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H84" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I84" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J84" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K84" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L84" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M84" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B85" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C85" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D85" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E85" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F85" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G85" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H85" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I85" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J85" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K85" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L85" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M85" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B86" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C86" t="s">
         <v>15</v>
@@ -5390,7 +5397,7 @@
         <v>16</v>
       </c>
       <c r="E86" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F86" t="s">
         <v>18</v>
@@ -5405,65 +5412,65 @@
         <v>21</v>
       </c>
       <c r="J86" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K86" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L86" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M86" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B87" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C87" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D87" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E87" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F87" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G87" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H87" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I87" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J87" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K87" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L87" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M87" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B88" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C88" t="s">
         <v>15</v>
@@ -5487,24 +5494,24 @@
         <v>21</v>
       </c>
       <c r="J88" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K88" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L88" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M88" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B89" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C89" t="s">
         <v>15</v>
@@ -5513,7 +5520,7 @@
         <v>16</v>
       </c>
       <c r="E89" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F89" t="s">
         <v>18</v>
@@ -5528,147 +5535,147 @@
         <v>21</v>
       </c>
       <c r="J89" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K89" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L89" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M89" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B90" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C90" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D90" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E90" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F90" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G90" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H90" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I90" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J90" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K90" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L90" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M90" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B91" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C91" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D91" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E91" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F91" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G91" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H91" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I91" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J91" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K91" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L91" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M91" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B92" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C92" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D92" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E92" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F92" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G92" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H92" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I92" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J92" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K92" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L92" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M92" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B93" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C93" t="s">
         <v>15</v>
@@ -5677,7 +5684,7 @@
         <v>16</v>
       </c>
       <c r="E93" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F93" t="s">
         <v>18</v>
@@ -5692,106 +5699,106 @@
         <v>21</v>
       </c>
       <c r="J93" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K93" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L93" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M93" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B94" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C94" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D94" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E94" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F94" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G94" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H94" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I94" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J94" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K94" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L94" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M94" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B95" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C95" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D95" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E95" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F95" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G95" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H95" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I95" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J95" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K95" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L95" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M95" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B96" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C96" t="s">
         <v>15</v>
@@ -5800,7 +5807,7 @@
         <v>16</v>
       </c>
       <c r="E96" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F96" t="s">
         <v>18</v>
@@ -5815,106 +5822,106 @@
         <v>21</v>
       </c>
       <c r="J96" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K96" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L96" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M96" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B97" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C97" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D97" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E97" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F97" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G97" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H97" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I97" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J97" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K97" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L97" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M97" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B98" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C98" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D98" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E98" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F98" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G98" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H98" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I98" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J98" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K98" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L98" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M98" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B99" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C99" t="s">
         <v>15</v>
@@ -5938,106 +5945,106 @@
         <v>21</v>
       </c>
       <c r="J99" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K99" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L99" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M99" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B100" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C100" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D100" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E100" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F100" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G100" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H100" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I100" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J100" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K100" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L100" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M100" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B101" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C101" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D101" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E101" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F101" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G101" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H101" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I101" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J101" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K101" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L101" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M101" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B102" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C102" t="s">
         <v>15</v>
@@ -6061,106 +6068,106 @@
         <v>21</v>
       </c>
       <c r="J102" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K102" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L102" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M102" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B103" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C103" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D103" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E103" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F103" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G103" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H103" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I103" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J103" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K103" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L103" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M103" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B104" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C104" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D104" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E104" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F104" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G104" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H104" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I104" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J104" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K104" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L104" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M104" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B105" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C105" t="s">
         <v>15</v>
@@ -6184,106 +6191,106 @@
         <v>21</v>
       </c>
       <c r="J105" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K105" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L105" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M105" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B106" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C106" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D106" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E106" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F106" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G106" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H106" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I106" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J106" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K106" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L106" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M106" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B107" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C107" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D107" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E107" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F107" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G107" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H107" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I107" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J107" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K107" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L107" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M107" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B108" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C108" t="s">
         <v>15</v>
@@ -6307,106 +6314,106 @@
         <v>21</v>
       </c>
       <c r="J108" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K108" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L108" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M108" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B109" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C109" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D109" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E109" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F109" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G109" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H109" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I109" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J109" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K109" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L109" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M109" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B110" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C110" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D110" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E110" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F110" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G110" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H110" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I110" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J110" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K110" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L110" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M110" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B111" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C111" t="s">
         <v>15</v>
@@ -6415,7 +6422,7 @@
         <v>16</v>
       </c>
       <c r="E111" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F111" t="s">
         <v>18</v>
@@ -6430,147 +6437,147 @@
         <v>21</v>
       </c>
       <c r="J111" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K111" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L111" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M111" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B112" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C112" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D112" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E112" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F112" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G112" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H112" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I112" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J112" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K112" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L112" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M112" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B113" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C113" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D113" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E113" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F113" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G113" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H113" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I113" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J113" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K113" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L113" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M113" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B114" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C114" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D114" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E114" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F114" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G114" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H114" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I114" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J114" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K114" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L114" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M114" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B115" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C115" t="s">
         <v>15</v>
@@ -6594,106 +6601,106 @@
         <v>21</v>
       </c>
       <c r="J115" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K115" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L115" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M115" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B116" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C116" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D116" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E116" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F116" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G116" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H116" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I116" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J116" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K116" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L116" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M116" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B117" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C117" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D117" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E117" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F117" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G117" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H117" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I117" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J117" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K117" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L117" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M117" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B118" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C118" t="s">
         <v>15</v>
@@ -6717,106 +6724,106 @@
         <v>21</v>
       </c>
       <c r="J118" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K118" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L118" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M118" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B119" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C119" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D119" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E119" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F119" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G119" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H119" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I119" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J119" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K119" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L119" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M119" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B120" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C120" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D120" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E120" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F120" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G120" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H120" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I120" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J120" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K120" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L120" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M120" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B121" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C121" t="s">
         <v>15</v>
@@ -6840,106 +6847,106 @@
         <v>21</v>
       </c>
       <c r="J121" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K121" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L121" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M121" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B122" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C122" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D122" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E122" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F122" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G122" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H122" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I122" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J122" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K122" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L122" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M122" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B123" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C123" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D123" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E123" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F123" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G123" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H123" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I123" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J123" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K123" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L123" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M123" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B124" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C124" t="s">
         <v>15</v>
@@ -6963,106 +6970,106 @@
         <v>21</v>
       </c>
       <c r="J124" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K124" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L124" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M124" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B125" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C125" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D125" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E125" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F125" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G125" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H125" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I125" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J125" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K125" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L125" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M125" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B126" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C126" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D126" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E126" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F126" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G126" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H126" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I126" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J126" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K126" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L126" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M126" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B127" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C127" t="s">
         <v>15</v>
@@ -7071,7 +7078,7 @@
         <v>16</v>
       </c>
       <c r="E127" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F127" t="s">
         <v>18</v>
@@ -7086,229 +7093,229 @@
         <v>21</v>
       </c>
       <c r="J127" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K127" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L127" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M127" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B128" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C128" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D128" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E128" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F128" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G128" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H128" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I128" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J128" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K128" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L128" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M128" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B129" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C129" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D129" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E129" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F129" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G129" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H129" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I129" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J129" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K129" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L129" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M129" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B130" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C130" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D130" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E130" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F130" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G130" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H130" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I130" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J130" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K130" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L130" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M130" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B131" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C131" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D131" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E131" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F131" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G131" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H131" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I131" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J131" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K131" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L131" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M131" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B132" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C132" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D132" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E132" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F132" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G132" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H132" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I132" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J132" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K132" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L132" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M132" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B133" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C133" t="s">
         <v>15</v>
@@ -7332,106 +7339,106 @@
         <v>21</v>
       </c>
       <c r="J133" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K133" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L133" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M133" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B134" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C134" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D134" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E134" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F134" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G134" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H134" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I134" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J134" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K134" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L134" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M134" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B135" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C135" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D135" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E135" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F135" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G135" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H135" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I135" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J135" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K135" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L135" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M135" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B136" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C136" t="s">
         <v>15</v>
@@ -7455,106 +7462,106 @@
         <v>21</v>
       </c>
       <c r="J136" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K136" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L136" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M136" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B137" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C137" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D137" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E137" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F137" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G137" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H137" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I137" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J137" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K137" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L137" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M137" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B138" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C138" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D138" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E138" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F138" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G138" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H138" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I138" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J138" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K138" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L138" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M138" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B139" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C139" t="s">
         <v>15</v>
@@ -7563,7 +7570,7 @@
         <v>16</v>
       </c>
       <c r="E139" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F139" t="s">
         <v>18</v>
@@ -7578,229 +7585,229 @@
         <v>21</v>
       </c>
       <c r="J139" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K139" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L139" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M139" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B140" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C140" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D140" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E140" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F140" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G140" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H140" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I140" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J140" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K140" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L140" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M140" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B141" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C141" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D141" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E141" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F141" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G141" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H141" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I141" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J141" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K141" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L141" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M141" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B142" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C142" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D142" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E142" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F142" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G142" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H142" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I142" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J142" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K142" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L142" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M142" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B143" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C143" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D143" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E143" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F143" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G143" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H143" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I143" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J143" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K143" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L143" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M143" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B144" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C144" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D144" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E144" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F144" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G144" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H144" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I144" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J144" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K144" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L144" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M144" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B145" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C145" t="s">
         <v>15</v>
@@ -7809,7 +7816,7 @@
         <v>16</v>
       </c>
       <c r="E145" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F145" t="s">
         <v>18</v>
@@ -7824,147 +7831,147 @@
         <v>21</v>
       </c>
       <c r="J145" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K145" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L145" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M145" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B146" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C146" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D146" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E146" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F146" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G146" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H146" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I146" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J146" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K146" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L146" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M146" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B147" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C147" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D147" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E147" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F147" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G147" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H147" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I147" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J147" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K147" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L147" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M147" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B148" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C148" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D148" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E148" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F148" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G148" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H148" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I148" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J148" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K148" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L148" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M148" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B149" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C149" t="s">
         <v>15</v>
@@ -7988,106 +7995,106 @@
         <v>21</v>
       </c>
       <c r="J149" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K149" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L149" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M149" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B150" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C150" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D150" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E150" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F150" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G150" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H150" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I150" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J150" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K150" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L150" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M150" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B151" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C151" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D151" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E151" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F151" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G151" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H151" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I151" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J151" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K151" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L151" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M151" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B152" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C152" t="s">
         <v>15</v>
@@ -8111,106 +8118,106 @@
         <v>21</v>
       </c>
       <c r="J152" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K152" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L152" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M152" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B153" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C153" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D153" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E153" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F153" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G153" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H153" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I153" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J153" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K153" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L153" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M153" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B154" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C154" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D154" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E154" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F154" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G154" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H154" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I154" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J154" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K154" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L154" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M154" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B155" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C155" t="s">
         <v>15</v>
@@ -8234,106 +8241,106 @@
         <v>21</v>
       </c>
       <c r="J155" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K155" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L155" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M155" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B156" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C156" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D156" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E156" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F156" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G156" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H156" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I156" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J156" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K156" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L156" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M156" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B157" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C157" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D157" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E157" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F157" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G157" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H157" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I157" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J157" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K157" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L157" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M157" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B158" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C158" t="s">
         <v>15</v>
@@ -8357,106 +8364,106 @@
         <v>21</v>
       </c>
       <c r="J158" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K158" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L158" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M158" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B159" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C159" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D159" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E159" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F159" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G159" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H159" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I159" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J159" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K159" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L159" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M159" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B160" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C160" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D160" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E160" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F160" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G160" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H160" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I160" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J160" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K160" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L160" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M160" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B161" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C161" t="s">
         <v>15</v>
@@ -8465,7 +8472,7 @@
         <v>16</v>
       </c>
       <c r="E161" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F161" t="s">
         <v>18</v>
@@ -8477,232 +8484,232 @@
         <v>20</v>
       </c>
       <c r="I161" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J161" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K161" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L161" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M161" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B162" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C162" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D162" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E162" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F162" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G162" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H162" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I162" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J162" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K162" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L162" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M162" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B163" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C163" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D163" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E163" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F163" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G163" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H163" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I163" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J163" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K163" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L163" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M163" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B164" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C164" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D164" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E164" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F164" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G164" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H164" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I164" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J164" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K164" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L164" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M164" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B165" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C165" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D165" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E165" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F165" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G165" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H165" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I165" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J165" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K165" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L165" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M165" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B166" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C166" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D166" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E166" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F166" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G166" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H166" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I166" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J166" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K166" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L166" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M166" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B167" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C167" t="s">
         <v>15</v>
@@ -8726,229 +8733,229 @@
         <v>21</v>
       </c>
       <c r="J167" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L167" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M167" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B168" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C168" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D168" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E168" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F168" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G168" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H168" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I168" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J168" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L168" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M168" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B169" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C169" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D169" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E169" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F169" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G169" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H169" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I169" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J169" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K169" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L169" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M169" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B170" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C170" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D170" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E170" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F170" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G170" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H170" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I170" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J170" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K170" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L170" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M170" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B171" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C171" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D171" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E171" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F171" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G171" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H171" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I171" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J171" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K171" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L171" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M171" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B172" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C172" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D172" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E172" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F172" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G172" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H172" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I172" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J172" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K172" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L172" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M172" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B173" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C173" t="s">
         <v>15</v>
@@ -8972,188 +8979,188 @@
         <v>21</v>
       </c>
       <c r="J173" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K173" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L173" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M173" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B174" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C174" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D174" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E174" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F174" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G174" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H174" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I174" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J174" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K174" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L174" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M174" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B175" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C175" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D175" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E175" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F175" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G175" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H175" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I175" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J175" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K175" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L175" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M175" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B176" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C176" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D176" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E176" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F176" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G176" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H176" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I176" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J176" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K176" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L176" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M176" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B177" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C177" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D177" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E177" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F177" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G177" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H177" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I177" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J177" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K177" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M177" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="178" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B178" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C178" t="s">
         <v>15</v>
@@ -9177,106 +9184,106 @@
         <v>21</v>
       </c>
       <c r="J178" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K178" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L178" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M178" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B179" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C179" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D179" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E179" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F179" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G179" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H179" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I179" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J179" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K179" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L179" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M179" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B180" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C180" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D180" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E180" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F180" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G180" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H180" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I180" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J180" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K180" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L180" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M180" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B181" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C181" t="s">
         <v>15</v>
@@ -9300,221 +9307,237 @@
         <v>21</v>
       </c>
       <c r="J181" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K181" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L181" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M181" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="182" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B182" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C182" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D182" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E182" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F182" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G182" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H182" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I182" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J182" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K182" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L182" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M182" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B183" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C183" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D183" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E183" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F183" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G183" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H183" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I183" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J183" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K183" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L183" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M183" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B184" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C184" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D184" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E184" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F184" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G184" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H184" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I184" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J184" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K184" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L184" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M184" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B185" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C185" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D185" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E185" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F185" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G185" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H185" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I185" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J185" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K185" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L185" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M185" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I187" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J187" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K187" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L187" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M187" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>477</v>
       </c>
     </row>
   </sheetData>

--- a/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
@@ -1495,7 +1495,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>18ff78cd3fbd5f1eaea8671aab16ad4934208919e92d0cf838fb3049b31c1e53</t>
+    <t>6729770ff2e77acf7dfad5e1019f025e9612e9fa3d5a8ea5b9a5f4adb8ffb470</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
@@ -1495,7 +1495,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>6729770ff2e77acf7dfad5e1019f025e9612e9fa3d5a8ea5b9a5f4adb8ffb470</t>
+    <t>216e3ef472e1d1a5fd8bdc823b2299e2983f8e64bb024549c10be824c756f7bc</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
@@ -1495,7 +1495,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>216e3ef472e1d1a5fd8bdc823b2299e2983f8e64bb024549c10be824c756f7bc</t>
+    <t>277fceb9bb3698d9453fc43411968cd91d3f9449455906d5d23de81a08ec2170</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
@@ -1495,7 +1495,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>f9d696e3767564ce556785ab32c8d4d620422045a781f574890b1a82aec41d64</t>
+    <t>57a96ebc2a9427589cbb7cc0296e9f637c842c12b7f8c8e0ccb6cf435e12d27f</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
@@ -1495,7 +1495,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>57a96ebc2a9427589cbb7cc0296e9f637c842c12b7f8c8e0ccb6cf435e12d27f</t>
+    <t>e654a4f812c4ac1bbbd49bec0a6a66cc601c73fe4374e6e441effe43a9071f32</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
@@ -1495,7 +1495,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>277fceb9bb3698d9453fc43411968cd91d3f9449455906d5d23de81a08ec2170</t>
+    <t>380d8e0d585bd783101a2b952772f0a3767a293b55ceefd229d969fdbd06bb46</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
@@ -1495,7 +1495,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>380d8e0d585bd783101a2b952772f0a3767a293b55ceefd229d969fdbd06bb46</t>
+    <t>cac2701a5bdd1841a1d0e7e6b5d664c8adc61c2fa348a93419b1f3051fe19823</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
@@ -1495,7 +1495,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>cac2701a5bdd1841a1d0e7e6b5d664c8adc61c2fa348a93419b1f3051fe19823</t>
+    <t>f28c807cfb6eeb8b94ac190190f1358c8dc4f8c37d5142ffe46b461a0507db07</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
@@ -1495,7 +1495,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>f28c807cfb6eeb8b94ac190190f1358c8dc4f8c37d5142ffe46b461a0507db07</t>
+    <t>d96ccb59875274442c18342f06a9aa9c3097f6ed8a4e1cb1fd5e32267acbe42c</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
@@ -1495,7 +1495,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>d96ccb59875274442c18342f06a9aa9c3097f6ed8a4e1cb1fd5e32267acbe42c</t>
+    <t>49b6bbaa1b0534e99f83598cc30c0c62ecee0b835796d356c2fde35f8e610e29</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
@@ -1495,7 +1495,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>49b6bbaa1b0534e99f83598cc30c0c62ecee0b835796d356c2fde35f8e610e29</t>
+    <t>a5f7d6500d58722995e66601ec026824ea3e350a07badce9343a7a492d496f36</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
@@ -1495,7 +1495,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>a5f7d6500d58722995e66601ec026824ea3e350a07badce9343a7a492d496f36</t>
+    <t>636a977849267dc2016113abf29c1c780ee08ec327c6f8ab32a1e036b3a6cf92</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
@@ -1495,7 +1495,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>636a977849267dc2016113abf29c1c780ee08ec327c6f8ab32a1e036b3a6cf92</t>
+    <t>9b801757218047b86420f352cec3e581306b4bdd9151437dfc89dac28f323abc</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-core.xlsx
@@ -5,14 +5,13 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="corporate_override_core" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="__fp__" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2419" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2418" uniqueCount="477">
   <si>
     <t>TC ID</t>
   </si>
@@ -1493,9 +1492,6 @@
   </si>
   <si>
     <t>Last Updated: 2026-07-31</t>
-  </si>
-  <si>
-    <t>9b801757218047b86420f352cec3e581306b4bdd9151437dfc89dac28f323abc</t>
   </si>
 </sst>
 </file>
@@ -9528,20 +9524,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>477</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
 </file>